--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Grants'!$A$4:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Grants'!$A$4:$M$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -619,7 +619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Youth</t>
+          <t>Youth outreach</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Housing support</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Meals</t>
+          <t>Community meals</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -649,7 +649,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Digital literacy</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -659,7 +659,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mind</t>
+          <t>Mental health first aid</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -669,7 +669,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Volunteer coordinator</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -752,7 +752,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>G-101 Youth outreach grant</t>
+          <t>Youth outreach grant</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
@@ -769,7 +769,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>G-102 Housing support grant</t>
+          <t>Housing support grant</t>
         </is>
       </c>
       <c r="B7" s="14" t="n">
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>G-103 Community meals grant</t>
+          <t>Community meals grant</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
@@ -803,7 +803,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>G-104 Digital literacy grant</t>
+          <t>Digital literacy grant</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
@@ -820,7 +820,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>G-105 Mental health first aid grant</t>
+          <t>Mental health first aid grant</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
@@ -837,7 +837,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>G-106 Volunteer coordinator grant</t>
+          <t>Volunteer coordinator grant</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
@@ -1815,12 +1815,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -1831,7 +1831,6 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1851,70 +1850,65 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Program</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
           <t>Funder</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
           <t>End</t>
         </is>
       </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Received to date</t>
+        </is>
+      </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>Received to date</t>
+          <t>Spent to date</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>Spent to date</t>
+          <t>Spent Aug</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Spent Aug</t>
+          <t>Spent Sep</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>Spent Sep</t>
+          <t>Budget to date</t>
         </is>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Spend vs budget %</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>Spend vs budget %</t>
+          <t>Still to spend</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
-        <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="N4" s="21" t="inlineStr">
         <is>
           <t>Months left</t>
         </is>
@@ -1923,329 +1917,299 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G-101</t>
+          <t>Youth outreach</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Youth outreach</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>State Department of Families</t>
         </is>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="C5" s="22" t="n">
         <v>480000</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>2027-06-30</t>
         </is>
       </c>
+      <c r="F5" s="22" t="n">
+        <v>300000</v>
+      </c>
       <c r="G5" s="22" t="n">
+        <v>306300</v>
+      </c>
+      <c r="H5" s="22" t="n">
+        <v>21500</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>22800</v>
+      </c>
+      <c r="J5" s="22" t="n">
         <v>300000</v>
       </c>
-      <c r="H5" s="22" t="n">
-        <v>306300</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>21500</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <v>22800</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>300000</v>
-      </c>
-      <c r="L5" s="8" t="n">
+      <c r="K5" s="8" t="n">
         <v>102.1</v>
       </c>
+      <c r="L5" s="22" t="n">
+        <v>173700</v>
+      </c>
       <c r="M5" s="22" t="n">
-        <v>173700</v>
-      </c>
-      <c r="N5" s="22" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G-102</t>
+          <t>Housing support</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Housing support</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>State Housing Program</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="C6" s="22" t="n">
         <v>360000</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>2026-12-31</t>
         </is>
       </c>
+      <c r="F6" s="22" t="n">
+        <v>360000</v>
+      </c>
       <c r="G6" s="22" t="n">
-        <v>360000</v>
+        <v>257700</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>257700</v>
+        <v>30500</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>30500</v>
+        <v>31200</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>31200</v>
-      </c>
-      <c r="K6" s="22" t="n">
         <v>270000</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="K6" s="8" t="n">
         <v>95.40000000000001</v>
       </c>
+      <c r="L6" s="22" t="n">
+        <v>102300</v>
+      </c>
       <c r="M6" s="22" t="n">
-        <v>102300</v>
-      </c>
-      <c r="N6" s="22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G-103</t>
+          <t>Community meals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Community meals</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>Local council community grant</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="C7" s="22" t="n">
         <v>48000</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>2027-06-30</t>
         </is>
       </c>
+      <c r="F7" s="22" t="n">
+        <v>48000</v>
+      </c>
       <c r="G7" s="22" t="n">
-        <v>48000</v>
+        <v>12000</v>
       </c>
       <c r="H7" s="22" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>4300</v>
+      </c>
+      <c r="J7" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="I7" s="22" t="n">
-        <v>4100</v>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>4300</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L7" s="8" t="n">
+      <c r="K7" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="L7" s="22" t="n">
+        <v>36000</v>
+      </c>
       <c r="M7" s="22" t="n">
-        <v>36000</v>
-      </c>
-      <c r="N7" s="22" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G-104</t>
+          <t>Digital literacy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Digital literacy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>Philanthropic foundation</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="C8" s="22" t="n">
         <v>90000</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>2027-03-31</t>
         </is>
       </c>
+      <c r="F8" s="22" t="n">
+        <v>45000</v>
+      </c>
       <c r="G8" s="22" t="n">
-        <v>45000</v>
+        <v>59600</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>59600</v>
+        <v>5200</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>5200</v>
+        <v>4900</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>4900</v>
-      </c>
-      <c r="K8" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="8" t="n">
         <v>99.3</v>
       </c>
+      <c r="L8" s="22" t="n">
+        <v>30400</v>
+      </c>
       <c r="M8" s="22" t="n">
-        <v>30400</v>
-      </c>
-      <c r="N8" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-105</t>
+          <t>Mental health first aid</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mental health first aid</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>Federal health program</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="C9" s="22" t="n">
         <v>120000</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>2027-03-31</t>
         </is>
       </c>
+      <c r="F9" s="22" t="n">
+        <v>60000</v>
+      </c>
       <c r="G9" s="22" t="n">
+        <v>57200</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>9400</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <v>10800</v>
+      </c>
+      <c r="J9" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="H9" s="22" t="n">
-        <v>57200</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>9400</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>10800</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>60000</v>
-      </c>
-      <c r="L9" s="8" t="n">
+      <c r="K9" s="8" t="n">
         <v>95.3</v>
       </c>
+      <c r="L9" s="22" t="n">
+        <v>62800</v>
+      </c>
       <c r="M9" s="22" t="n">
-        <v>62800</v>
-      </c>
-      <c r="N9" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G-106</t>
+          <t>Volunteer coordinator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Volunteer coordinator</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>State volunteering grant</t>
         </is>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="C10" s="22" t="n">
         <v>36000</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>2027-02-28</t>
         </is>
       </c>
+      <c r="F10" s="22" t="n">
+        <v>36000</v>
+      </c>
       <c r="G10" s="22" t="n">
-        <v>36000</v>
+        <v>21000</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>21000</v>
+        <v>3000</v>
       </c>
       <c r="I10" s="22" t="n">
         <v>3000</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K10" s="22" t="n">
         <v>21000</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="K10" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="L10" s="22" t="n">
+        <v>15000</v>
+      </c>
       <c r="M10" s="22" t="n">
-        <v>15000</v>
-      </c>
-      <c r="N10" s="22" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N10"/>
+  <autoFilter ref="A4:M10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2330,7 +2294,7 @@
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>G-101 Youth outreach</t>
+          <t>Youth outreach</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
@@ -2342,7 +2306,7 @@
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>G-102 Housing support</t>
+          <t>Housing support</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
@@ -2354,7 +2318,7 @@
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>G-103 Community meals</t>
+          <t>Community meals</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
@@ -2366,7 +2330,7 @@
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>G-104 Digital literacy</t>
+          <t>Digital literacy</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
@@ -2378,7 +2342,7 @@
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>G-105 Mental health first aid</t>
+          <t>Mental health first aid</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
@@ -2390,7 +2354,7 @@
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>G-106 Volunteer coordinator</t>
+          <t>Volunteer coordinator</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">

--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -11,11 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PandL" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grants" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grants" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Grants'!$A$4:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Grants'!$A$4:$M$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -122,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,13 +158,20 @@
     <xf numFmtId="165" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
     </xf>
@@ -612,7 +620,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Grant spend vs budget to date (%)</t>
+          <t>Grant spend to date against budget</t>
         </is>
       </c>
     </row>
@@ -1810,6 +1818,1810 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C172"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>How each number is worked out</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · generated 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Cost to raise a dollar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Fundraising costs ÷ money raised (grants, donations, events)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr"/>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Grant writing and reporting</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>$7,100</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>$7,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Donor campaigns</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>$5,400</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>$2,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Event costs</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>$16,900</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>$2,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Fundraising costs</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>$29,400</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>$11,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Grant income</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>$77,000</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>$73,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>$27,900</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>$18,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Fundraising events</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>$41,600</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Money raised</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>$146,500</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>$92,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Cost per dollar raised</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>20¢</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>13¢</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>September's gala raised $41,600 but cost $16,900 to run, which lifts the month's figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Unrestricted cash runway</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>(Cash at bank − unspent grant money) ÷ this month's cash spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr"/>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Cash at bank</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>$480,780</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>$525,675</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Less unspent grant money (belongs to funders' programs)</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>$-156,100</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>$-221,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Unrestricted cash</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>$324,680</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>$303,775</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Cash spending in the month (expenses less depreciation)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>$162,900</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>$141,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Runway</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>2.0 months</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>2.2 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Reserves target: 3 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Grants ending in the next 6 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Grant total − spent to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr"/>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Ends</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Housing support</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>31 Dec 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>$102,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Volunteer coordinator</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>28 Feb 2027</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>$15,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr"/>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>$117,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Unspent money usually has to be returned, or an extension negotiated, so plan the spending now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Youth outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>State Department of Families · $480,000 · Jul 2025 to Jun 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr"/>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>$300,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>$173,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>$306,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>$300,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>Spent against budget</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>102.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="n">
+        <v>17363</v>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aug 25</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n">
+        <v>21144</v>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="n">
+        <v>17537</v>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="n">
+        <v>21925</v>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="n">
+        <v>21079</v>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="n">
+        <v>19272</v>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="n">
+        <v>21157</v>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="n">
+        <v>20743</v>
+      </c>
+      <c r="C58" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="n">
+        <v>16515</v>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="n">
+        <v>20451</v>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="n">
+        <v>21174</v>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="n">
+        <v>20366</v>
+      </c>
+      <c r="C62" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="n">
+        <v>23274</v>
+      </c>
+      <c r="C63" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B64" s="23" t="n">
+        <v>21500</v>
+      </c>
+      <c r="C64" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="n">
+        <v>22800</v>
+      </c>
+      <c r="C65" s="23" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Housing support</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>State Housing Program · $360,000 · Jan 2026 to Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr"/>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>$360,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>$102,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="21" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>$257,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>$270,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
+        <is>
+          <t>Spent against budget</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>95.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="B80" s="23" t="n">
+        <v>30502</v>
+      </c>
+      <c r="C80" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="n">
+        <v>26508</v>
+      </c>
+      <c r="C81" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B82" s="23" t="n">
+        <v>24832</v>
+      </c>
+      <c r="C82" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="n">
+        <v>23730</v>
+      </c>
+      <c r="C83" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B84" s="23" t="n">
+        <v>31337</v>
+      </c>
+      <c r="C84" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="n">
+        <v>29994</v>
+      </c>
+      <c r="C85" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B86" s="23" t="n">
+        <v>29097</v>
+      </c>
+      <c r="C86" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="n">
+        <v>30500</v>
+      </c>
+      <c r="C87" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B88" s="23" t="n">
+        <v>31200</v>
+      </c>
+      <c r="C88" s="23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Community meals</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Local council community grant · $48,000 · Jul 2026 to Jun 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20" t="inlineStr"/>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="inlineStr">
+        <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>$48,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>$36,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>$12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>$12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>Spent against budget</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C103" s="23" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C104" s="23" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="n">
+        <v>4300</v>
+      </c>
+      <c r="C105" s="23" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Digital literacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Philanthropic foundation · $90,000 · Oct 2025 to Mar 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr"/>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="inlineStr">
+        <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>$45,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="21" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>$30,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B114" s="22" t="inlineStr">
+        <is>
+          <t>$59,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B115" s="22" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="inlineStr">
+        <is>
+          <t>Spent against budget</t>
+        </is>
+      </c>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>99.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C119" s="20" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="n">
+        <v>5160</v>
+      </c>
+      <c r="C120" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="n">
+        <v>4585</v>
+      </c>
+      <c r="C121" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="n">
+        <v>5221</v>
+      </c>
+      <c r="C122" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="n">
+        <v>4426</v>
+      </c>
+      <c r="C123" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="n">
+        <v>5408</v>
+      </c>
+      <c r="C124" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B125" s="23" t="n">
+        <v>5427</v>
+      </c>
+      <c r="C125" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B126" s="23" t="n">
+        <v>5509</v>
+      </c>
+      <c r="C126" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B127" s="23" t="n">
+        <v>4635</v>
+      </c>
+      <c r="C127" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="n">
+        <v>4316</v>
+      </c>
+      <c r="C128" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="n">
+        <v>4813</v>
+      </c>
+      <c r="C129" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C130" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B131" s="23" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C131" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Mental health first aid</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Federal health program · $120,000 · Apr 2026 to Mar 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr"/>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="21" t="inlineStr">
+        <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B137" s="22" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="21" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>$62,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="21" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B139" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B140" s="22" t="inlineStr">
+        <is>
+          <t>$57,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B141" s="22" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="21" t="inlineStr">
+        <is>
+          <t>Spent against budget</t>
+        </is>
+      </c>
+      <c r="B142" s="22" t="inlineStr">
+        <is>
+          <t>95.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C145" s="20" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B146" s="23" t="n">
+        <v>9584</v>
+      </c>
+      <c r="C146" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B147" s="23" t="n">
+        <v>8950</v>
+      </c>
+      <c r="C147" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B148" s="23" t="n">
+        <v>9797</v>
+      </c>
+      <c r="C148" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B149" s="23" t="n">
+        <v>8669</v>
+      </c>
+      <c r="C149" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B150" s="23" t="n">
+        <v>9400</v>
+      </c>
+      <c r="C150" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B151" s="23" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C151" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>State volunteering grant · $36,000 · Mar 2026 to Feb 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20" t="inlineStr"/>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="21" t="inlineStr">
+        <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B157" s="22" t="inlineStr">
+        <is>
+          <t>$36,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="21" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B158" s="22" t="inlineStr">
+        <is>
+          <t>$15,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="21" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B159" s="22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B160" s="22" t="inlineStr">
+        <is>
+          <t>$21,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B161" s="22" t="inlineStr">
+        <is>
+          <t>$21,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="21" t="inlineStr">
+        <is>
+          <t>Spent against budget</t>
+        </is>
+      </c>
+      <c r="B162" s="22" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B165" s="20" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C165" s="20" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B166" s="23" t="n">
+        <v>2932</v>
+      </c>
+      <c r="C166" s="23" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B167" s="23" t="n">
+        <v>3555</v>
+      </c>
+      <c r="C167" s="23" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B168" s="23" t="n">
+        <v>2649</v>
+      </c>
+      <c r="C168" s="23" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B169" s="23" t="n">
+        <v>2699</v>
+      </c>
+      <c r="C169" s="23" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B170" s="23" t="n">
+        <v>3165</v>
+      </c>
+      <c r="C170" s="23" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B171" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C171" s="23" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B172" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C172" s="23" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1848,67 +3660,67 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Funder</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Received to date</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>Spent Aug</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>Spent Sep</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Spend vs budget %</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Months left</t>
         </is>
@@ -1925,7 +3737,7 @@
           <t>State Department of Families</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <v>480000</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -1938,28 +3750,28 @@
           <t>2027-06-30</t>
         </is>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="23" t="n">
         <v>300000</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="23" t="n">
         <v>306300</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="23" t="n">
         <v>21500</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="23" t="n">
         <v>22800</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="23" t="n">
         <v>300000</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>102.1</v>
       </c>
-      <c r="L5" s="22" t="n">
+      <c r="L5" s="23" t="n">
         <v>173700</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="M5" s="23" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1974,7 +3786,7 @@
           <t>State Housing Program</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>360000</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1987,28 +3799,28 @@
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="23" t="n">
         <v>360000</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="23" t="n">
         <v>257700</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="23" t="n">
         <v>31200</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="23" t="n">
         <v>270000</v>
       </c>
       <c r="K6" s="8" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="L6" s="22" t="n">
+      <c r="L6" s="23" t="n">
         <v>102300</v>
       </c>
-      <c r="M6" s="22" t="n">
+      <c r="M6" s="23" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2023,7 +3835,7 @@
           <t>Local council community grant</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>48000</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -2036,28 +3848,28 @@
           <t>2027-06-30</t>
         </is>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="23" t="n">
         <v>48000</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="23" t="n">
         <v>12000</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="23" t="n">
         <v>4100</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="23" t="n">
         <v>4300</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="23" t="n">
         <v>12000</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="L7" s="22" t="n">
+      <c r="L7" s="23" t="n">
         <v>36000</v>
       </c>
-      <c r="M7" s="22" t="n">
+      <c r="M7" s="23" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2072,7 +3884,7 @@
           <t>Philanthropic foundation</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>90000</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -2085,28 +3897,28 @@
           <t>2027-03-31</t>
         </is>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="23" t="n">
         <v>45000</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="23" t="n">
         <v>59600</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="23" t="n">
         <v>5200</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="23" t="n">
         <v>4900</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="23" t="n">
         <v>60000</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="L8" s="22" t="n">
+      <c r="L8" s="23" t="n">
         <v>30400</v>
       </c>
-      <c r="M8" s="22" t="n">
+      <c r="M8" s="23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2121,7 +3933,7 @@
           <t>Federal health program</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>120000</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -2134,28 +3946,28 @@
           <t>2027-03-31</t>
         </is>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="23" t="n">
         <v>60000</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="23" t="n">
         <v>57200</v>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="23" t="n">
         <v>9400</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="23" t="n">
         <v>10800</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="23" t="n">
         <v>60000</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>95.3</v>
       </c>
-      <c r="L9" s="22" t="n">
+      <c r="L9" s="23" t="n">
         <v>62800</v>
       </c>
-      <c r="M9" s="22" t="n">
+      <c r="M9" s="23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2170,7 +3982,7 @@
           <t>State volunteering grant</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>36000</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -2183,28 +3995,28 @@
           <t>2027-02-28</t>
         </is>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>36000</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="23" t="n">
         <v>21000</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="23" t="n">
         <v>3000</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="23" t="n">
         <v>3000</v>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="23" t="n">
         <v>21000</v>
       </c>
       <c r="K10" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="L10" s="22" t="n">
+      <c r="L10" s="23" t="n">
         <v>15000</v>
       </c>
-      <c r="M10" s="22" t="n">
+      <c r="M10" s="23" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2214,7 +4026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2249,36 +4061,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>A Brisbane community services charity funded by six grants, donations, events and program fees. About 18 staff. Registered charity, income-tax exempt.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Reporting month</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>September 2026, compared with August 2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Financial year</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>FY2027: 1 July 2026 to 30 June 2027</t>
         </is>
@@ -2292,96 +4104,96 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>State Department of Families: $480,000, 2025-07 to 2027-06</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>State Housing Program: $360,000, 2026-01 to 2026-12</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Local council community grant: $48,000, 2026-07 to 2027-06</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Philanthropic foundation: $90,000, 2025-10 to 2027-03</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Federal health program: $120,000, 2026-04 to 2027-03</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>State volunteering grant: $36,000, 2026-03 to 2027-02</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Grant income</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>recognised as the money is spent on the program</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Unspent grants</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>instalments received but not yet spent are a liability (grants received in advance)</t>
         </is>
@@ -2395,48 +4207,48 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>including the spring appeal in September</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Fundraising event</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>September gala: income and costs in the same month</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Grant-funded spending</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>75% wages, the rest program costs</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>none: registered charity, income-tax exempt</t>
         </is>
@@ -2450,60 +4262,60 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Suppliers</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>paid the following month</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>cash at bank less unspent grant money</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Cash runway</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>unrestricted cash ÷ this month's cash spending</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Reserves target</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>3 months of spending</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>excluded throughout, for simplicity</t>
         </is>

--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -16,7 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PandL'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Grants'!$A$4:$M$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Grants'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +545,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -566,6 +570,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -647,11 +658,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Community meals</t>
+          <t>Mental health first aid</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="12">
@@ -667,11 +678,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mental health first aid</t>
+          <t>Community meals</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>95.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -695,7 +706,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -728,6 +749,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1238,8 +1266,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1272,6 +1309,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1537,8 +1581,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1571,6 +1624,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1812,8 +1872,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1821,7 +1890,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1845,6 +1914,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2084,12 +2160,12 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>$-156,100</t>
+          <t>($156,100)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>$-221,900</t>
+          <t>($221,900)</t>
         </is>
       </c>
     </row>
@@ -2783,14 +2859,14 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Community meals</t>
+          <t>Mental health first aid</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>Local council community grant · $48,000 · Jul 2026 to Jun 2027</t>
+          <t>Federal health program · $120,000 · Apr 2026 to Mar 2027</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2886,7 @@
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>$48,000</t>
+          <t>$60,000</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2898,7 @@
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>$36,000</t>
+          <t>$62,800</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2910,7 @@
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2922,7 @@
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>$12,000</t>
+          <t>$57,200</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2934,7 @@
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>$12,000</t>
+          <t>$60,000</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2946,7 @@
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>95.3%</t>
         </is>
       </c>
     </row>
@@ -2901,207 +2977,207 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B103" s="23" t="n">
-        <v>3600</v>
+        <v>9584</v>
       </c>
       <c r="C103" s="23" t="n">
-        <v>4000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B104" s="23" t="n">
-        <v>4100</v>
+        <v>8950</v>
       </c>
       <c r="C104" s="23" t="n">
-        <v>4000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="n">
+        <v>9797</v>
+      </c>
+      <c r="C105" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="n">
+        <v>8669</v>
+      </c>
+      <c r="C106" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B107" s="23" t="n">
+        <v>9400</v>
+      </c>
+      <c r="C107" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B105" s="23" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C105" s="23" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="B108" s="23" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C108" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>Philanthropic foundation · $90,000 · Oct 2025 to Mar 2027</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr"/>
-      <c r="B110" s="20" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr"/>
+      <c r="B113" s="20" t="inlineStr">
         <is>
           <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="21" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B111" s="22" t="inlineStr">
-        <is>
-          <t>$45,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="21" t="inlineStr">
-        <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B112" s="22" t="inlineStr">
-        <is>
-          <t>$30,400</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="21" t="inlineStr">
-        <is>
-          <t>Months left</t>
-        </is>
-      </c>
-      <c r="B113" s="22" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="21" t="inlineStr">
         <is>
-          <t>Spent to date</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B114" s="22" t="inlineStr">
         <is>
-          <t>$59,600</t>
+          <t>$45,000</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="21" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Still to spend</t>
         </is>
       </c>
       <c r="B115" s="22" t="inlineStr">
         <is>
-          <t>$60,000</t>
+          <t>$30,400</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
         <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B117" s="22" t="inlineStr">
+        <is>
+          <t>$59,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B118" s="22" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="inlineStr">
+        <is>
           <t>Spent against budget</t>
         </is>
       </c>
-      <c r="B116" s="22" t="inlineStr">
+      <c r="B119" s="22" t="inlineStr">
         <is>
           <t>99.3%</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="7" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B119" s="20" t="inlineStr">
+      <c r="B122" s="20" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C119" s="20" t="inlineStr">
+      <c r="C122" s="20" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Oct 25</t>
-        </is>
-      </c>
-      <c r="B120" s="23" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C120" s="23" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Nov 25</t>
-        </is>
-      </c>
-      <c r="B121" s="23" t="n">
-        <v>4585</v>
-      </c>
-      <c r="C121" s="23" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Dec 25</t>
-        </is>
-      </c>
-      <c r="B122" s="23" t="n">
-        <v>5221</v>
-      </c>
-      <c r="C122" s="23" t="n">
-        <v>5000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jan 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B123" s="23" t="n">
-        <v>4426</v>
+        <v>5160</v>
       </c>
       <c r="C123" s="23" t="n">
         <v>5000</v>
@@ -3110,11 +3186,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B124" s="23" t="n">
-        <v>5408</v>
+        <v>4585</v>
       </c>
       <c r="C124" s="23" t="n">
         <v>5000</v>
@@ -3123,11 +3199,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Dec 25</t>
         </is>
       </c>
       <c r="B125" s="23" t="n">
-        <v>5427</v>
+        <v>5221</v>
       </c>
       <c r="C125" s="23" t="n">
         <v>5000</v>
@@ -3136,11 +3212,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Jan 26</t>
         </is>
       </c>
       <c r="B126" s="23" t="n">
-        <v>5509</v>
+        <v>4426</v>
       </c>
       <c r="C126" s="23" t="n">
         <v>5000</v>
@@ -3149,11 +3225,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B127" s="23" t="n">
-        <v>4635</v>
+        <v>5408</v>
       </c>
       <c r="C127" s="23" t="n">
         <v>5000</v>
@@ -3162,11 +3238,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B128" s="23" t="n">
-        <v>4316</v>
+        <v>5427</v>
       </c>
       <c r="C128" s="23" t="n">
         <v>5000</v>
@@ -3175,11 +3251,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B129" s="23" t="n">
-        <v>4813</v>
+        <v>5509</v>
       </c>
       <c r="C129" s="23" t="n">
         <v>5000</v>
@@ -3188,11 +3264,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B130" s="23" t="n">
-        <v>5200</v>
+        <v>4635</v>
       </c>
       <c r="C130" s="23" t="n">
         <v>5000</v>
@@ -3201,171 +3277,171 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B131" s="23" t="n">
-        <v>4900</v>
+        <v>4316</v>
       </c>
       <c r="C131" s="23" t="n">
         <v>5000</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="n">
+        <v>4813</v>
+      </c>
+      <c r="C132" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B133" s="23" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C133" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>Mental health first aid</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Federal health program · $120,000 · Apr 2026 to Mar 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="20" t="inlineStr"/>
-      <c r="B136" s="20" t="inlineStr">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B134" s="23" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C134" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Community meals</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>Local council community grant · $48,000 · Jul 2026 to Jun 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr"/>
+      <c r="B139" s="20" t="inlineStr">
         <is>
           <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="21" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B137" s="22" t="inlineStr">
-        <is>
-          <t>$60,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="21" t="inlineStr">
-        <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B138" s="22" t="inlineStr">
-        <is>
-          <t>$62,800</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="21" t="inlineStr">
-        <is>
-          <t>Months left</t>
-        </is>
-      </c>
-      <c r="B139" s="22" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="21" t="inlineStr">
         <is>
-          <t>Spent to date</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B140" s="22" t="inlineStr">
         <is>
-          <t>$57,200</t>
+          <t>$48,000</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="21" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Still to spend</t>
         </is>
       </c>
       <c r="B141" s="22" t="inlineStr">
         <is>
-          <t>$60,000</t>
+          <t>$36,000</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="21" t="inlineStr">
         <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B142" s="22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B143" s="22" t="inlineStr">
+        <is>
+          <t>$12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="21" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>$12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="21" t="inlineStr">
+        <is>
           <t>Spent against budget</t>
         </is>
       </c>
-      <c r="B142" s="22" t="inlineStr">
-        <is>
-          <t>95.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
+      <c r="B145" s="22" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="20" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B145" s="20" t="inlineStr">
+      <c r="B148" s="20" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C145" s="20" t="inlineStr">
+      <c r="C148" s="20" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B146" s="23" t="n">
-        <v>9584</v>
-      </c>
-      <c r="C146" s="23" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="B147" s="23" t="n">
-        <v>8950</v>
-      </c>
-      <c r="C147" s="23" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B148" s="23" t="n">
-        <v>9797</v>
-      </c>
-      <c r="C148" s="23" t="n">
-        <v>10000</v>
       </c>
     </row>
     <row r="149">
@@ -3375,10 +3451,10 @@
         </is>
       </c>
       <c r="B149" s="23" t="n">
-        <v>8669</v>
+        <v>3600</v>
       </c>
       <c r="C149" s="23" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="150">
@@ -3388,10 +3464,10 @@
         </is>
       </c>
       <c r="B150" s="23" t="n">
-        <v>9400</v>
+        <v>4100</v>
       </c>
       <c r="C150" s="23" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="151">
@@ -3401,10 +3477,10 @@
         </is>
       </c>
       <c r="B151" s="23" t="n">
-        <v>10800</v>
+        <v>4300</v>
       </c>
       <c r="C151" s="23" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="154">
@@ -3617,7 +3693,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3625,7 +3711,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3659,6 +3745,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -4022,7 +4115,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:M10"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4030,7 +4133,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4053,6 +4156,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -4371,6 +4481,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -37,57 +37,69 @@
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="169" formatCode="d mmm yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="002F7A5D"/>
@@ -134,35 +146,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -173,24 +185,24 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
     </xf>
@@ -798,8 +810,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 nfp-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1370,8 +1382,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 nfp-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1696,8 +1708,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 nfp-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1995,8 +2007,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 nfp-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2448,8 +2460,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 nfp-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4581,8 +4593,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 nfp-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5017,8 +5029,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 nfp-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -163,7 +163,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
@@ -188,6 +187,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -681,14 +681,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Each grant: spent to 30 September 2026 against budget to the same date</t>
+          <t>Each grant: over or under budget to 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Whole grant from its start date. Budget to date = the grant spread evenly over its months.</t>
+          <t>Spending to date against budget to date (the grant spread evenly over its months). Over budget in red; under budget in grey.</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$ spent</t>
+          <t>$</t>
         </is>
       </c>
     </row>
@@ -712,11 +712,11 @@
         </is>
       </c>
       <c r="B14" s="9">
+        <f>Workings!B50</f>
+        <v/>
+      </c>
+      <c r="C14" s="7">
         <f>Workings!B49</f>
-        <v/>
-      </c>
-      <c r="C14" s="7">
-        <f>Workings!B45</f>
         <v/>
       </c>
     </row>
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="B15" s="9">
-        <f>Workings!B80</f>
+        <f>Workings!B82</f>
         <v/>
       </c>
       <c r="C15" s="7">
-        <f>Workings!B76</f>
+        <f>Workings!B81</f>
         <v/>
       </c>
     </row>
@@ -742,11 +742,11 @@
         </is>
       </c>
       <c r="B16" s="9">
-        <f>Workings!B105</f>
+        <f>Workings!B108</f>
         <v/>
       </c>
       <c r="C16" s="7">
-        <f>Workings!B101</f>
+        <f>Workings!B107</f>
         <v/>
       </c>
     </row>
@@ -757,11 +757,11 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>Workings!B127</f>
+        <f>Workings!B131</f>
         <v/>
       </c>
       <c r="C17" s="7">
-        <f>Workings!B123</f>
+        <f>Workings!B130</f>
         <v/>
       </c>
     </row>
@@ -772,11 +772,11 @@
         </is>
       </c>
       <c r="B18" s="9">
-        <f>Workings!B155</f>
+        <f>Workings!B160</f>
         <v/>
       </c>
       <c r="C18" s="7">
-        <f>Workings!B151</f>
+        <f>Workings!B159</f>
         <v/>
       </c>
     </row>
@@ -787,22 +787,12 @@
         </is>
       </c>
       <c r="B19" s="9">
-        <f>Workings!B174</f>
+        <f>Workings!B180</f>
         <v/>
       </c>
       <c r="C19" s="7">
-        <f>Workings!B170</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>1</v>
+        <f>Workings!B179</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -879,14 +869,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Youth outreach grant</t>
         </is>
@@ -897,13 +887,13 @@
       <c r="C6" s="7" t="n">
         <v>21500</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Housing support grant</t>
         </is>
@@ -914,13 +904,13 @@
       <c r="C7" s="7" t="n">
         <v>30500</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Community meals grant</t>
         </is>
@@ -931,13 +921,13 @@
       <c r="C8" s="7" t="n">
         <v>4100</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Digital literacy grant</t>
         </is>
@@ -948,13 +938,13 @@
       <c r="C9" s="7" t="n">
         <v>5200</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Mental health first aid grant</t>
         </is>
@@ -965,13 +955,13 @@
       <c r="C10" s="7" t="n">
         <v>9400</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Volunteer coordinator grant</t>
         </is>
@@ -982,13 +972,13 @@
       <c r="C11" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
@@ -999,13 +989,13 @@
       <c r="C12" s="7" t="n">
         <v>18400</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
@@ -1016,13 +1006,13 @@
       <c r="C13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>B13-C13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Program fees</t>
         </is>
@@ -1033,13 +1023,13 @@
       <c r="C14" s="7" t="n">
         <v>26800</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
@@ -1050,39 +1040,39 @@
       <c r="C15" s="7" t="n">
         <v>1450</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <f>B15-C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <f>SUM(B6:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <f>SUM(C6:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Grant-funded program wages</t>
         </is>
@@ -1093,13 +1083,13 @@
       <c r="C18" s="7" t="n">
         <v>-55275</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Grant-funded program costs</t>
         </is>
@@ -1110,13 +1100,13 @@
       <c r="C19" s="7" t="n">
         <v>-18425</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="12">
         <f>B19-C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Program delivery wages (untied)</t>
         </is>
@@ -1127,13 +1117,13 @@
       <c r="C20" s="7" t="n">
         <v>-14000</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="12">
         <f>B20-C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Program costs (untied)</t>
         </is>
@@ -1144,39 +1134,39 @@
       <c r="C21" s="7" t="n">
         <v>-5500</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <f>B21-C21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Total program spend</t>
         </is>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="14">
         <f>SUM(B18:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="14">
         <f>SUM(C18:C21)</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="15">
         <f>B22-C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Fundraising</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Grant writing and reporting</t>
         </is>
@@ -1187,13 +1177,13 @@
       <c r="C24" s="7" t="n">
         <v>-7100</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <f>B24-C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Donor campaigns</t>
         </is>
@@ -1204,13 +1194,13 @@
       <c r="C25" s="7" t="n">
         <v>-2200</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <f>B25-C25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Event costs</t>
         </is>
@@ -1221,39 +1211,39 @@
       <c r="C26" s="7" t="n">
         <v>-2400</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <f>B26-C26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Total fundraising costs</t>
         </is>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="14">
         <f>SUM(B24:B26)</f>
         <v/>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <f>SUM(C24:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="15">
         <f>B27-C27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Administration wages</t>
         </is>
@@ -1264,13 +1254,13 @@
       <c r="C29" s="7" t="n">
         <v>-18300</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="12">
         <f>B29-C29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
@@ -1281,13 +1271,13 @@
       <c r="C30" s="7" t="n">
         <v>-10000</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="12">
         <f>B30-C30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Other administration</t>
         </is>
@@ -1298,81 +1288,81 @@
       <c r="C31" s="7" t="n">
         <v>-8000</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="12">
         <f>B31-C31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Total administration</t>
         </is>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="14">
         <f>SUM(B29:B31)</f>
         <v/>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="14">
         <f>SUM(C29:C31)</f>
         <v/>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="15">
         <f>B32-C32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
+      <c r="B33" s="14" t="n">
         <v>-2900</v>
       </c>
-      <c r="C33" s="15" t="n">
+      <c r="C33" s="14" t="n">
         <v>-2900</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="15">
         <f>B33-C33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="14">
         <f>B22+B27+B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="14">
         <f>C22+C27+C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="15">
         <f>B34-C34</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Surplus for the month</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="17">
         <f>B16+B34</f>
         <v/>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="17">
         <f>C16+C34</f>
         <v/>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="18">
         <f>B35-C35</f>
         <v/>
       </c>
@@ -1454,14 +1444,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Current assets</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
@@ -1472,13 +1462,13 @@
       <c r="C6" s="7" t="n">
         <v>525675</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Program fees receivable</t>
         </is>
@@ -1489,13 +1479,13 @@
       <c r="C7" s="7" t="n">
         <v>9800</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Grants receivable (spent ahead of instalment)</t>
         </is>
@@ -1506,13 +1496,13 @@
       <c r="C8" s="7" t="n">
         <v>9700</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Prepayments</t>
         </is>
@@ -1523,75 +1513,75 @@
       <c r="C9" s="7" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Vehicles and equipment</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="14" t="n">
         <v>172200</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="14" t="n">
         <v>175100</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <f>B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Current liabilities</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Payables (bills due next month)</t>
         </is>
@@ -1602,13 +1592,13 @@
       <c r="C14" s="7" t="n">
         <v>46525</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Grants received in advance (unspent)</t>
         </is>
@@ -1619,13 +1609,13 @@
       <c r="C15" s="7" t="n">
         <v>221900</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <f>B15-C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Employee leave provisions</t>
         </is>
@@ -1636,69 +1626,69 @@
       <c r="C16" s="7" t="n">
         <v>165900</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <f>SUM(B14:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <f>SUM(C14:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <f>B17-C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Net assets</t>
         </is>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <f>B12-B17</f>
         <v/>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <f>C12-C17</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="18">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Accumulated funds</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="17" t="n">
         <v>317330</v>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="17" t="n">
         <v>306950</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="18">
         <f>B20-C20</f>
         <v/>
       </c>
@@ -1777,14 +1767,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Operating activities</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Grant instalments received</t>
         </is>
@@ -1795,13 +1785,13 @@
       <c r="C6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Donations and fundraising received</t>
         </is>
@@ -1812,13 +1802,13 @@
       <c r="C7" s="7" t="n">
         <v>18400</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Program fees received</t>
         </is>
@@ -1829,13 +1819,13 @@
       <c r="C8" s="7" t="n">
         <v>26100</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Interest received</t>
         </is>
@@ -1846,13 +1836,13 @@
       <c r="C9" s="7" t="n">
         <v>1450</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Payments to suppliers</t>
         </is>
@@ -1863,13 +1853,13 @@
       <c r="C10" s="7" t="n">
         <v>-36500</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Payments to employees</t>
         </is>
@@ -1880,39 +1870,39 @@
       <c r="C11" s="7" t="n">
         <v>-93775</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <f>SUM(B6:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Investing activities</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Purchase of vehicles and equipment</t>
         </is>
@@ -1923,81 +1913,81 @@
       <c r="C14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Net cash from investing activities</t>
         </is>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <f>SUM(B14:B14)</f>
         <v/>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <f>SUM(C14:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <f>B15-C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <f>B12+B15</f>
         <v/>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <f>C12+C15</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Cash at start of month</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="14" t="n">
         <v>525675</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="14" t="n">
         <v>610000</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <f>B17-C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Cash at end of month</t>
         </is>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <f>B17+B16</f>
         <v/>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <f>C17+C16</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="18">
         <f>B18-C18</f>
         <v/>
       </c>
@@ -2138,318 +2128,318 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>State Department of Families</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="20" t="n">
         <v>480000</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="21" t="n">
         <v>45839</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="21" t="n">
         <v>46568</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="20" t="n">
         <v>300000</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="20" t="n">
         <v>306300</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="20" t="n">
         <v>21500</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="20" t="n">
         <v>22800</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="20" t="n">
         <v>300000</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="22">
         <f>IF(J7=0,"",G7/J7)</f>
         <v/>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="20">
         <f>C7-G7</f>
         <v/>
       </c>
-      <c r="M7" s="21" t="n">
+      <c r="M7" s="20" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>State Housing Program</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="20" t="n">
         <v>360000</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="21" t="n">
         <v>46023</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="20" t="n">
         <v>360000</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="20" t="n">
         <v>257700</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="20" t="n">
         <v>30500</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="20" t="n">
         <v>31200</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="20" t="n">
         <v>270000</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="22">
         <f>IF(J8=0,"",G8/J8)</f>
         <v/>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="20">
         <f>C8-G8</f>
         <v/>
       </c>
-      <c r="M8" s="21" t="n">
+      <c r="M8" s="20" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Federal health program</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="20" t="n">
         <v>120000</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="21" t="n">
         <v>46113</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="21" t="n">
         <v>46477</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="20" t="n">
         <v>60000</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="20" t="n">
         <v>57200</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="20" t="n">
         <v>9400</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="20" t="n">
         <v>10800</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="20" t="n">
         <v>60000</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="22">
         <f>IF(J9=0,"",G9/J9)</f>
         <v/>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="20">
         <f>C9-G9</f>
         <v/>
       </c>
-      <c r="M9" s="21" t="n">
+      <c r="M9" s="20" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Philanthropic foundation</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="20" t="n">
         <v>90000</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="21" t="n">
         <v>45931</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="21" t="n">
         <v>46477</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="20" t="n">
         <v>45000</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <v>59600</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="20" t="n">
         <v>5200</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="20" t="n">
         <v>4900</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="20" t="n">
         <v>60000</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="22">
         <f>IF(J10=0,"",G10/J10)</f>
         <v/>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="20">
         <f>C10-G10</f>
         <v/>
       </c>
-      <c r="M10" s="21" t="n">
+      <c r="M10" s="20" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Local council community grant</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="20" t="n">
         <v>48000</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="21" t="n">
         <v>46204</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="21" t="n">
         <v>46568</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="20" t="n">
         <v>48000</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="20" t="n">
         <v>12000</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="20" t="n">
         <v>4100</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="20" t="n">
         <v>4300</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="20" t="n">
         <v>12000</v>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="22">
         <f>IF(J11=0,"",G11/J11)</f>
         <v/>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="20">
         <f>C11-G11</f>
         <v/>
       </c>
-      <c r="M11" s="21" t="n">
+      <c r="M11" s="20" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>State volunteering grant</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="20" t="n">
         <v>36000</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="21" t="n">
         <v>46082</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="21" t="n">
         <v>46446</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="20" t="n">
         <v>36000</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="20" t="n">
         <v>21000</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="20" t="n">
         <v>21000</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="22">
         <f>IF(J12=0,"",G12/J12)</f>
         <v/>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="20">
         <f>C12-G12</f>
         <v/>
       </c>
-      <c r="M12" s="21" t="n">
+      <c r="M12" s="20" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <f>SUM(C7:C12)</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <f>SUM(F7:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <f>SUM(G7:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <f>SUM(H7:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <f>SUM(I7:I12)</f>
         <v/>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="24">
         <f>SUM(J7:J12)</f>
         <v/>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="24">
         <f>SUM(L7:L12)</f>
         <v/>
       </c>
@@ -2476,7 +2466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D188"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2508,14 +2498,14 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Cost to raise a dollar</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Fundraising costs ÷ money raised (grants, donations, events), in cents</t>
         </is>
@@ -2540,10 +2530,10 @@
           <t>Grant writing and reporting</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="20" t="n">
         <v>7100</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="20" t="n">
         <v>7100</v>
       </c>
     </row>
@@ -2553,10 +2543,10 @@
           <t>Donor campaigns</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="20" t="n">
         <v>5400</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="20" t="n">
         <v>2200</v>
       </c>
     </row>
@@ -2566,10 +2556,10 @@
           <t>Event costs</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="20" t="n">
         <v>16900</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="20" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -2579,11 +2569,11 @@
           <t>Fundraising costs</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <f>B8+B9+B10</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="20">
         <f>C8+C9+C10</f>
         <v/>
       </c>
@@ -2594,10 +2584,10 @@
           <t>Grant income</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="20" t="n">
         <v>77000</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="20" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -2607,10 +2597,10 @@
           <t>Donations</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="20" t="n">
         <v>27900</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="20" t="n">
         <v>18400</v>
       </c>
     </row>
@@ -2620,10 +2610,10 @@
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="20" t="n">
         <v>41600</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2633,11 +2623,11 @@
           <t>Money raised</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <f>B12+B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <f>C12+C13+C14</f>
         <v/>
       </c>
@@ -2667,14 +2657,14 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Unrestricted cash runway</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>(Cash at bank − unspent grant money) ÷ this month's cash spending</t>
         </is>
@@ -2699,10 +2689,10 @@
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="20" t="n">
         <v>480780</v>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="20" t="n">
         <v>525675</v>
       </c>
     </row>
@@ -2712,10 +2702,10 @@
           <t>Less unspent grant money (belongs to funders' programs)</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="20" t="n">
         <v>-156100</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="20" t="n">
         <v>-221900</v>
       </c>
     </row>
@@ -2725,11 +2715,11 @@
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <f>B23+B24</f>
         <v/>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="20">
         <f>C23+C24</f>
         <v/>
       </c>
@@ -2740,10 +2730,10 @@
           <t>Cash spending in the month (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="20" t="n">
         <v>162900</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="20" t="n">
         <v>141200</v>
       </c>
     </row>
@@ -2772,14 +2762,14 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>Grants ending in the next 6 months</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Grant total − spent to date, for each grant ending soon</t>
         </is>
@@ -2799,7 +2789,7 @@
           <t>Housing support (ends 31 Dec 2026)</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="20" t="n">
         <v>102300</v>
       </c>
     </row>
@@ -2809,7 +2799,7 @@
           <t>Volunteer coordinator (ends 28 Feb 2027)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
+      <c r="B35" s="20" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -2834,14 +2824,14 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>State Department of Families · $480,000 · Jul 2025 to Jun 2027</t>
         </is>
@@ -2861,7 +2851,7 @@
           <t>Grant total</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
+      <c r="B43" s="20" t="n">
         <v>480000</v>
       </c>
     </row>
@@ -2871,7 +2861,7 @@
           <t>Received from the funder</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
+      <c r="B44" s="20" t="n">
         <v>300000</v>
       </c>
     </row>
@@ -2881,7 +2871,7 @@
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
+      <c r="B45" s="20" t="n">
         <v>306300</v>
       </c>
     </row>
@@ -2891,7 +2881,7 @@
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="B46" s="21" t="n">
+      <c r="B46" s="20" t="n">
         <v>300000</v>
       </c>
     </row>
@@ -2901,7 +2891,7 @@
           <t>Months left</t>
         </is>
       </c>
-      <c r="B47" s="21" t="n">
+      <c r="B47" s="20" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2911,77 +2901,71 @@
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="20">
         <f>B43-B45</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Spent against budget</t>
-        </is>
-      </c>
-      <c r="B49" s="31">
-        <f>B45/B46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Over (under) budget to date</t>
+        </is>
+      </c>
+      <c r="B49" s="20">
+        <f>B45-B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>Over (under) budget, % of budget to date</t>
+        </is>
+      </c>
+      <c r="B50" s="31">
+        <f>B45/B46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Jul 25</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="n">
-        <v>17363</v>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D53" s="9">
-        <f>IF(C53=0,"",B53/C53)</f>
-        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Aug 25</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>21144</v>
+        <v>17363</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>20000</v>
@@ -2994,11 +2978,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>Aug 25</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>17537</v>
+        <v>21144</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>20000</v>
@@ -3011,11 +2995,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>21925</v>
+        <v>17537</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>20000</v>
@@ -3028,11 +3012,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>21079</v>
+        <v>21925</v>
       </c>
       <c r="C57" s="7" t="n">
         <v>20000</v>
@@ -3045,11 +3029,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dec 25</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>19272</v>
+        <v>21079</v>
       </c>
       <c r="C58" s="7" t="n">
         <v>20000</v>
@@ -3062,11 +3046,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jan 26</t>
+          <t>Dec 25</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>21157</v>
+        <v>19272</v>
       </c>
       <c r="C59" s="7" t="n">
         <v>20000</v>
@@ -3079,11 +3063,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Jan 26</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>20743</v>
+        <v>21157</v>
       </c>
       <c r="C60" s="7" t="n">
         <v>20000</v>
@@ -3096,11 +3080,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>16515</v>
+        <v>20743</v>
       </c>
       <c r="C61" s="7" t="n">
         <v>20000</v>
@@ -3113,11 +3097,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>20451</v>
+        <v>16515</v>
       </c>
       <c r="C62" s="7" t="n">
         <v>20000</v>
@@ -3130,11 +3114,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>21174</v>
+        <v>20451</v>
       </c>
       <c r="C63" s="7" t="n">
         <v>20000</v>
@@ -3147,11 +3131,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>20366</v>
+        <v>21174</v>
       </c>
       <c r="C64" s="7" t="n">
         <v>20000</v>
@@ -3164,11 +3148,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>23274</v>
+        <v>20366</v>
       </c>
       <c r="C65" s="7" t="n">
         <v>20000</v>
@@ -3181,11 +3165,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>21500</v>
+        <v>23274</v>
       </c>
       <c r="C66" s="7" t="n">
         <v>20000</v>
@@ -3198,11 +3182,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Aug 26</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>22800</v>
+        <v>21500</v>
       </c>
       <c r="C67" s="7" t="n">
         <v>20000</v>
@@ -3213,192 +3197,186 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>22800</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D68" s="9">
+        <f>IF(C68=0,"",B68/C68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B68" s="32">
-        <f>SUM(B53:B67)</f>
-        <v/>
-      </c>
-      <c r="C68" s="32">
-        <f>SUM(C53:C67)</f>
-        <v/>
-      </c>
-      <c r="D68" s="33">
-        <f>IF(C68=0,"",B68/C68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69"/>
+      <c r="B69" s="32">
+        <f>SUM(B54:B68)</f>
+        <v/>
+      </c>
+      <c r="C69" s="32">
+        <f>SUM(C54:C68)</f>
+        <v/>
+      </c>
+      <c r="D69" s="33">
+        <f>IF(C69=0,"",B69/C69)</f>
+        <v/>
+      </c>
+    </row>
     <row r="70"/>
-    <row r="71">
-      <c r="A71" s="26" t="inlineStr">
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="25" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="26" t="inlineStr">
         <is>
           <t>State Housing Program · $360,000 · Jan 2026 to Dec 2026</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr"/>
-      <c r="B73" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr"/>
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B74" s="21" t="n">
-        <v>360000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B75" s="21" t="n">
+          <t>Grant total</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n">
         <v>360000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B76" s="21" t="n">
-        <v>257700</v>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="n">
+        <v>360000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Budget to date</t>
-        </is>
-      </c>
-      <c r="B77" s="21" t="n">
-        <v>270000</v>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n">
+        <v>257700</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Months left</t>
-        </is>
-      </c>
-      <c r="B78" s="21" t="n">
-        <v>3</v>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="n">
+        <v>270000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B79" s="21">
-        <f>B74-B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="27" t="inlineStr">
-        <is>
-          <t>Spent against budget</t>
-        </is>
-      </c>
-      <c r="B80" s="31">
-        <f>B76/B77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81"/>
+      <c r="B80" s="20">
+        <f>B75-B77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Over (under) budget to date</t>
+        </is>
+      </c>
+      <c r="B81" s="20">
+        <f>B77-B78</f>
+        <v/>
+      </c>
+    </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>Over (under) budget, % of budget to date</t>
+        </is>
+      </c>
+      <c r="B82" s="31">
+        <f>B77/B78-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Jan 26</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="n">
-        <v>30502</v>
-      </c>
-      <c r="C84" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D84" s="9">
-        <f>IF(C84=0,"",B84/C84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Feb 26</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="n">
-        <v>26508</v>
-      </c>
-      <c r="C85" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D85" s="9">
-        <f>IF(C85=0,"",B85/C85)</f>
-        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Jan 26</t>
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>24832</v>
+        <v>30502</v>
       </c>
       <c r="C86" s="7" t="n">
         <v>30000</v>
@@ -3411,11 +3389,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
-        <v>23730</v>
+        <v>26508</v>
       </c>
       <c r="C87" s="7" t="n">
         <v>30000</v>
@@ -3428,11 +3406,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B88" s="7" t="n">
-        <v>31337</v>
+        <v>24832</v>
       </c>
       <c r="C88" s="7" t="n">
         <v>30000</v>
@@ -3445,11 +3423,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>29994</v>
+        <v>23730</v>
       </c>
       <c r="C89" s="7" t="n">
         <v>30000</v>
@@ -3462,11 +3440,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>29097</v>
+        <v>31337</v>
       </c>
       <c r="C90" s="7" t="n">
         <v>30000</v>
@@ -3479,11 +3457,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
-        <v>30500</v>
+        <v>29994</v>
       </c>
       <c r="C91" s="7" t="n">
         <v>30000</v>
@@ -3496,11 +3474,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="B92" s="7" t="n">
-        <v>31200</v>
+        <v>29097</v>
       </c>
       <c r="C92" s="7" t="n">
         <v>30000</v>
@@ -3511,209 +3489,203 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="inlineStr">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>30500</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D93" s="9">
+        <f>IF(C93=0,"",B93/C93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>31200</v>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D94" s="9">
+        <f>IF(C94=0,"",B94/C94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B93" s="32">
-        <f>SUM(B84:B92)</f>
-        <v/>
-      </c>
-      <c r="C93" s="32">
-        <f>SUM(C84:C92)</f>
-        <v/>
-      </c>
-      <c r="D93" s="33">
-        <f>IF(C93=0,"",B93/C93)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+      <c r="B95" s="32">
+        <f>SUM(B86:B94)</f>
+        <v/>
+      </c>
+      <c r="C95" s="32">
+        <f>SUM(C86:C94)</f>
+        <v/>
+      </c>
+      <c r="D95" s="33">
+        <f>IF(C95=0,"",B95/C95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="25" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="26" t="inlineStr">
         <is>
           <t>Federal health program · $120,000 · Apr 2026 to Mar 2027</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr"/>
-      <c r="B98" s="4" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr"/>
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B99" s="21" t="n">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B100" s="21" t="n">
-        <v>60000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B101" s="21" t="n">
-        <v>57200</v>
+          <t>Grant total</t>
+        </is>
+      </c>
+      <c r="B101" s="20" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Budget to date</t>
-        </is>
-      </c>
-      <c r="B102" s="21" t="n">
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Months left</t>
-        </is>
-      </c>
-      <c r="B103" s="21" t="n">
-        <v>6</v>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n">
+        <v>57200</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B104" s="21">
-        <f>B99-B101</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="27" t="inlineStr">
-        <is>
-          <t>Spent against budget</t>
-        </is>
-      </c>
-      <c r="B105" s="31">
-        <f>B101/B102</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106"/>
+      <c r="B106" s="20">
+        <f>B101-B103</f>
+        <v/>
+      </c>
+    </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Over (under) budget to date</t>
+        </is>
+      </c>
+      <c r="B107" s="20">
+        <f>B103-B104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>Over (under) budget, % of budget to date</t>
+        </is>
+      </c>
+      <c r="B108" s="31">
+        <f>B103/B104-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="n">
-        <v>9584</v>
-      </c>
-      <c r="C109" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D109" s="9">
-        <f>IF(C109=0,"",B109/C109)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="n">
-        <v>8950</v>
-      </c>
-      <c r="C110" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D110" s="9">
-        <f>IF(C110=0,"",B110/C110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="n">
-        <v>9797</v>
-      </c>
-      <c r="C111" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D111" s="9">
-        <f>IF(C111=0,"",B111/C111)</f>
-        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B112" s="7" t="n">
-        <v>8669</v>
+        <v>9584</v>
       </c>
       <c r="C112" s="7" t="n">
         <v>10000</v>
@@ -3726,11 +3698,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B113" s="7" t="n">
-        <v>9400</v>
+        <v>8950</v>
       </c>
       <c r="C113" s="7" t="n">
         <v>10000</v>
@@ -3743,11 +3715,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B114" s="7" t="n">
-        <v>10800</v>
+        <v>9797</v>
       </c>
       <c r="C114" s="7" t="n">
         <v>10000</v>
@@ -3758,226 +3730,220 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="24" t="inlineStr">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="n">
+        <v>8669</v>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D115" s="9">
+        <f>IF(C115=0,"",B115/C115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="n">
+        <v>9400</v>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D116" s="9">
+        <f>IF(C116=0,"",B116/C116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D117" s="9">
+        <f>IF(C117=0,"",B117/C117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B115" s="32">
-        <f>SUM(B109:B114)</f>
-        <v/>
-      </c>
-      <c r="C115" s="32">
-        <f>SUM(C109:C114)</f>
-        <v/>
-      </c>
-      <c r="D115" s="33">
-        <f>IF(C115=0,"",B115/C115)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118">
-      <c r="A118" s="26" t="inlineStr">
+      <c r="B118" s="32">
+        <f>SUM(B112:B117)</f>
+        <v/>
+      </c>
+      <c r="C118" s="32">
+        <f>SUM(C112:C117)</f>
+        <v/>
+      </c>
+      <c r="D118" s="33">
+        <f>IF(C118=0,"",B118/C118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" s="25" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="10" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="26" t="inlineStr">
         <is>
           <t>Philanthropic foundation · $90,000 · Oct 2025 to Mar 2027</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr"/>
-      <c r="B120" s="4" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr"/>
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B121" s="21" t="n">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B122" s="21" t="n">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B123" s="21" t="n">
-        <v>59600</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Budget to date</t>
-        </is>
-      </c>
-      <c r="B124" s="21" t="n">
-        <v>60000</v>
+          <t>Grant total</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Months left</t>
-        </is>
-      </c>
-      <c r="B125" s="21" t="n">
-        <v>6</v>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B125" s="20" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="n">
+        <v>59600</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B126" s="21">
-        <f>B121-B123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="27" t="inlineStr">
-        <is>
-          <t>Spent against budget</t>
-        </is>
-      </c>
-      <c r="B127" s="31">
-        <f>B123/B124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128"/>
-    <row r="129">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="B129" s="20">
+        <f>B124-B126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Over (under) budget to date</t>
+        </is>
+      </c>
+      <c r="B130" s="20">
+        <f>B126-B127</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t>Over (under) budget, % of budget to date</t>
+        </is>
+      </c>
+      <c r="B131" s="31">
+        <f>B126/B127-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Oct 25</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C131" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D131" s="9">
-        <f>IF(C131=0,"",B131/C131)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Nov 25</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="n">
-        <v>4585</v>
-      </c>
-      <c r="C132" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D132" s="9">
-        <f>IF(C132=0,"",B132/C132)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Dec 25</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="n">
-        <v>5221</v>
-      </c>
-      <c r="C133" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D133" s="9">
-        <f>IF(C133=0,"",B133/C133)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Jan 26</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="n">
-        <v>4426</v>
-      </c>
-      <c r="C134" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D134" s="9">
-        <f>IF(C134=0,"",B134/C134)</f>
-        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B135" s="7" t="n">
-        <v>5408</v>
+        <v>5160</v>
       </c>
       <c r="C135" s="7" t="n">
         <v>5000</v>
@@ -3990,11 +3956,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B136" s="7" t="n">
-        <v>5427</v>
+        <v>4585</v>
       </c>
       <c r="C136" s="7" t="n">
         <v>5000</v>
@@ -4007,11 +3973,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Dec 25</t>
         </is>
       </c>
       <c r="B137" s="7" t="n">
-        <v>5509</v>
+        <v>5221</v>
       </c>
       <c r="C137" s="7" t="n">
         <v>5000</v>
@@ -4024,11 +3990,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Jan 26</t>
         </is>
       </c>
       <c r="B138" s="7" t="n">
-        <v>4635</v>
+        <v>4426</v>
       </c>
       <c r="C138" s="7" t="n">
         <v>5000</v>
@@ -4041,11 +4007,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B139" s="7" t="n">
-        <v>4316</v>
+        <v>5408</v>
       </c>
       <c r="C139" s="7" t="n">
         <v>5000</v>
@@ -4058,11 +4024,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B140" s="7" t="n">
-        <v>4813</v>
+        <v>5427</v>
       </c>
       <c r="C140" s="7" t="n">
         <v>5000</v>
@@ -4075,11 +4041,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>5200</v>
+        <v>5509</v>
       </c>
       <c r="C141" s="7" t="n">
         <v>5000</v>
@@ -4092,11 +4058,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B142" s="7" t="n">
-        <v>4900</v>
+        <v>4635</v>
       </c>
       <c r="C142" s="7" t="n">
         <v>5000</v>
@@ -4107,456 +4073,444 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="24" t="inlineStr">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="n">
+        <v>4316</v>
+      </c>
+      <c r="C143" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D143" s="9">
+        <f>IF(C143=0,"",B143/C143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="n">
+        <v>4813</v>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D144" s="9">
+        <f>IF(C144=0,"",B144/C144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D145" s="9">
+        <f>IF(C145=0,"",B145/C145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D146" s="9">
+        <f>IF(C146=0,"",B146/C146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B143" s="32">
-        <f>SUM(B131:B142)</f>
-        <v/>
-      </c>
-      <c r="C143" s="32">
-        <f>SUM(C131:C142)</f>
-        <v/>
-      </c>
-      <c r="D143" s="33">
-        <f>IF(C143=0,"",B143/C143)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146">
-      <c r="A146" s="26" t="inlineStr">
+      <c r="B147" s="32">
+        <f>SUM(B135:B146)</f>
+        <v/>
+      </c>
+      <c r="C147" s="32">
+        <f>SUM(C135:C146)</f>
+        <v/>
+      </c>
+      <c r="D147" s="33">
+        <f>IF(C147=0,"",B147/C147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150">
+      <c r="A150" s="25" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="10" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="26" t="inlineStr">
         <is>
           <t>Local council community grant · $48,000 · Jul 2026 to Jun 2027</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr"/>
-      <c r="B148" s="4" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr"/>
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B149" s="21" t="n">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B150" s="21" t="n">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B151" s="21" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Budget to date</t>
-        </is>
-      </c>
-      <c r="B152" s="21" t="n">
-        <v>12000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Months left</t>
-        </is>
-      </c>
-      <c r="B153" s="21" t="n">
-        <v>9</v>
+          <t>Grant total</t>
+        </is>
+      </c>
+      <c r="B153" s="20" t="n">
+        <v>48000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B154" s="20" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B155" s="20" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B156" s="20" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B157" s="20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B154" s="21">
-        <f>B149-B151</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="27" t="inlineStr">
-        <is>
-          <t>Spent against budget</t>
-        </is>
-      </c>
-      <c r="B155" s="31">
-        <f>B151/B152</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156"/>
-    <row r="157">
-      <c r="A157" s="8" t="inlineStr">
-        <is>
-          <t>Spend by month against budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>Spend against budget</t>
-        </is>
+      <c r="B158" s="20">
+        <f>B153-B155</f>
+        <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>Over (under) budget to date</t>
+        </is>
+      </c>
+      <c r="B159" s="20">
+        <f>B155-B156</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="27" t="inlineStr">
+        <is>
+          <t>Over (under) budget, % of budget to date</t>
+        </is>
+      </c>
+      <c r="B160" s="31">
+        <f>B155/B156-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Spend against budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B159" s="7" t="n">
+      <c r="B164" s="7" t="n">
         <v>3600</v>
       </c>
-      <c r="C159" s="7" t="n">
+      <c r="C164" s="7" t="n">
         <v>4000</v>
       </c>
-      <c r="D159" s="9">
-        <f>IF(C159=0,"",B159/C159)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="D164" s="9">
+        <f>IF(C164=0,"",B164/C164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B160" s="7" t="n">
+      <c r="B165" s="7" t="n">
         <v>4100</v>
       </c>
-      <c r="C160" s="7" t="n">
+      <c r="C165" s="7" t="n">
         <v>4000</v>
       </c>
-      <c r="D160" s="9">
-        <f>IF(C160=0,"",B160/C160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="D165" s="9">
+        <f>IF(C165=0,"",B165/C165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B161" s="7" t="n">
+      <c r="B166" s="7" t="n">
         <v>4300</v>
       </c>
-      <c r="C161" s="7" t="n">
+      <c r="C166" s="7" t="n">
         <v>4000</v>
       </c>
-      <c r="D161" s="9">
-        <f>IF(C161=0,"",B161/C161)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="24" t="inlineStr">
+      <c r="D166" s="9">
+        <f>IF(C166=0,"",B166/C166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B162" s="32">
-        <f>SUM(B159:B161)</f>
-        <v/>
-      </c>
-      <c r="C162" s="32">
-        <f>SUM(C159:C161)</f>
-        <v/>
-      </c>
-      <c r="D162" s="33">
-        <f>IF(C162=0,"",B162/C162)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165">
-      <c r="A165" s="26" t="inlineStr">
+      <c r="B167" s="32">
+        <f>SUM(B164:B166)</f>
+        <v/>
+      </c>
+      <c r="C167" s="32">
+        <f>SUM(C164:C166)</f>
+        <v/>
+      </c>
+      <c r="D167" s="33">
+        <f>IF(C167=0,"",B167/C167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170">
+      <c r="A170" s="25" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="10" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="26" t="inlineStr">
         <is>
           <t>State volunteering grant · $36,000 · Mar 2026 to Feb 2027</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr"/>
-      <c r="B167" s="4" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr"/>
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B168" s="21" t="n">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B169" s="21" t="n">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B170" s="21" t="n">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Budget to date</t>
-        </is>
-      </c>
-      <c r="B171" s="21" t="n">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Months left</t>
-        </is>
-      </c>
-      <c r="B172" s="21" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B173" s="21">
-        <f>B168-B170</f>
-        <v/>
+          <t>Grant total</t>
+        </is>
+      </c>
+      <c r="B173" s="20" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="27" t="inlineStr">
-        <is>
-          <t>Spent against budget</t>
-        </is>
-      </c>
-      <c r="B174" s="31">
-        <f>B170/B171</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Received from the funder</t>
+        </is>
+      </c>
+      <c r="B174" s="20" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B175" s="20" t="n">
+        <v>21000</v>
+      </c>
+    </row>
     <row r="176">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>Spend by month against budget</t>
-        </is>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B176" s="20" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>Spend against budget</t>
-        </is>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B177" s="20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Mar 26</t>
-        </is>
-      </c>
-      <c r="B178" s="7" t="n">
-        <v>2932</v>
-      </c>
-      <c r="C178" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D178" s="9">
-        <f>IF(C178=0,"",B178/C178)</f>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B178" s="20">
+        <f>B173-B175</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B179" s="7" t="n">
-        <v>3555</v>
-      </c>
-      <c r="C179" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D179" s="9">
-        <f>IF(C179=0,"",B179/C179)</f>
+          <t>Over (under) budget to date</t>
+        </is>
+      </c>
+      <c r="B179" s="20">
+        <f>B175-B176</f>
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="B180" s="7" t="n">
-        <v>2649</v>
-      </c>
-      <c r="C180" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D180" s="9">
-        <f>IF(C180=0,"",B180/C180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="n">
-        <v>2699</v>
-      </c>
-      <c r="C181" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D181" s="9">
-        <f>IF(C181=0,"",B181/C181)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A180" s="27" t="inlineStr">
+        <is>
+          <t>Over (under) budget, % of budget to date</t>
+        </is>
+      </c>
+      <c r="B180" s="31">
+        <f>B175/B176-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181"/>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Jul 26</t>
-        </is>
-      </c>
-      <c r="B182" s="7" t="n">
-        <v>3165</v>
-      </c>
-      <c r="C182" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D182" s="9">
-        <f>IF(C182=0,"",B182/C182)</f>
-        <v/>
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>Spend by month against budget</t>
+        </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Aug 26</t>
-        </is>
-      </c>
-      <c r="B183" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C183" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D183" s="9">
-        <f>IF(C183=0,"",B183/C183)</f>
-        <v/>
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>Spend against budget</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B184" s="7" t="n">
-        <v>3000</v>
+        <v>2932</v>
       </c>
       <c r="C184" s="7" t="n">
         <v>3000</v>
@@ -4567,27 +4521,129 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="24" t="inlineStr">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="n">
+        <v>3555</v>
+      </c>
+      <c r="C185" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D185" s="9">
+        <f>IF(C185=0,"",B185/C185)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="n">
+        <v>2649</v>
+      </c>
+      <c r="C186" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D186" s="9">
+        <f>IF(C186=0,"",B186/C186)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="n">
+        <v>2699</v>
+      </c>
+      <c r="C187" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D187" s="9">
+        <f>IF(C187=0,"",B187/C187)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="n">
+        <v>3165</v>
+      </c>
+      <c r="C188" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D188" s="9">
+        <f>IF(C188=0,"",B188/C188)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C189" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D189" s="9">
+        <f>IF(C189=0,"",B189/C189)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C190" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D190" s="9">
+        <f>IF(C190=0,"",B190/C190)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B185" s="32">
-        <f>SUM(B178:B184)</f>
-        <v/>
-      </c>
-      <c r="C185" s="32">
-        <f>SUM(C178:C184)</f>
-        <v/>
-      </c>
-      <c r="D185" s="33">
-        <f>IF(C185=0,"",B185/C185)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
+      <c r="B191" s="32">
+        <f>SUM(B184:B190)</f>
+        <v/>
+      </c>
+      <c r="C191" s="32">
+        <f>SUM(C184:C190)</f>
+        <v/>
+      </c>
+      <c r="D191" s="33">
+        <f>IF(C191=0,"",B191/C191)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4603,11 +4659,11 @@
   <rowBreaks count="7" manualBreakCount="7">
     <brk id="30" min="0" max="16383" man="1"/>
     <brk id="39" min="0" max="16383" man="1"/>
-    <brk id="70" min="0" max="16383" man="1"/>
-    <brk id="95" min="0" max="16383" man="1"/>
-    <brk id="117" min="0" max="16383" man="1"/>
-    <brk id="145" min="0" max="16383" man="1"/>
-    <brk id="164" min="0" max="16383" man="1"/>
+    <brk id="71" min="0" max="16383" man="1"/>
+    <brk id="97" min="0" max="16383" man="1"/>
+    <brk id="120" min="0" max="16383" man="1"/>
+    <brk id="149" min="0" max="16383" man="1"/>
+    <brk id="169" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -4648,7 +4704,7 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>The organisation</t>
         </is>
@@ -4692,7 +4748,7 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
@@ -4796,7 +4852,7 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Other income and costs</t>
         </is>
@@ -4852,7 +4908,7 @@
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Cash and balance sheet</t>
         </is>
@@ -4920,7 +4976,7 @@
     </row>
     <row r="32"/>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Checks (all passed)</t>
         </is>
@@ -4969,7 +5025,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Print check (done before this file was saved)</t>
         </is>

--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -688,7 +688,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Spending to date against budget to date (the grant spread evenly over its months). Over budget in red; under budget in grey.</t>
+          <t>Spending to date against budget to date (the grant spread evenly over its months). Over or under budget in red; within 1% in amber.</t>
         </is>
       </c>
     </row>

--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -16,12 +16,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="Cost_to_raise_a_dollar">'The fourth sheet'!$B$6</definedName>
+    <definedName name="Unrestricted_cash_runway">'The fourth sheet'!$B$7</definedName>
+    <definedName name="Grants_ending_in_6_months">'The fourth sheet'!$B$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'The fourth sheet'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'The fourth sheet'!$A$1:$D$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Income and expenditure'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Income and expenditure'!$A$1:$D$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Balance sheet'!$A$1:$D$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Grants'!$A$6:$M$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cash flow'!$A$1:$D$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Grants'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Grants'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A$1:$D$191</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Assumptions'!$A$1:$B$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,13 +38,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;¢&quot;;[Red](0&quot;¢&quot;)"/>
     <numFmt numFmtId="166" formatCode="0.0&quot; months&quot;;[Red](0.0&quot; months&quot;)"/>
     <numFmt numFmtId="167" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="169" formatCode="d mmm yyyy"/>
+    <numFmt numFmtId="168" formatCode="+0&quot;¢&quot;;(0&quot;¢&quot;);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="+0.0&quot; months&quot;;(0.0&quot; months&quot;);&quot;-&quot;"/>
+    <numFmt numFmtId="170" formatCode="+#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="172" formatCode="d mmm yyyy"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -148,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,7 +171,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,18 +181,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="12" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -213,6 +227,22 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Roboto"/>
+        <b val="1"/>
+        <color rgb="00B42318"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Roboto"/>
+        <b val="1"/>
+        <color rgb="002F7A5D"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -283,6 +313,338 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Each grant: over or under budget to 30 September 2026</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>% of budget</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'The fourth sheet'!$A$14:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'The fourth sheet'!$B$14:$B$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Spent against budget to date</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Spent against budget to date</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Grants'!$A$7:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grants'!$K$7:$K$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grants" displayName="Grants" ref="A6:M12" headerRowCount="1">
+  <autoFilter ref="A6:M12"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="Program"/>
+    <tableColumn id="2" name="Funder"/>
+    <tableColumn id="3" name="Grant total"/>
+    <tableColumn id="4" name="Start"/>
+    <tableColumn id="5" name="End"/>
+    <tableColumn id="6" name="Received to date"/>
+    <tableColumn id="7" name="Spent to date"/>
+    <tableColumn id="8" name="Spent Aug"/>
+    <tableColumn id="9" name="Spent Sep"/>
+    <tableColumn id="10" name="Budget to date"/>
+    <tableColumn id="11" name="Spent against budget"/>
+    <tableColumn id="12" name="Still to spend"/>
+    <tableColumn id="13" name="Months left"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -593,14 +955,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -641,7 +1003,7 @@
         <f>Workings!C16</f>
         <v/>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <f>B6-C6</f>
         <v/>
       </c>
@@ -652,15 +1014,15 @@
           <t>Unrestricted cash runway</t>
         </is>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <f>Workings!B27</f>
         <v/>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <f>Workings!C27</f>
         <v/>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="8">
         <f>B7-C7</f>
         <v/>
       </c>
@@ -671,7 +1033,7 @@
           <t>Grants ending in 6 months</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <f>Workings!B36</f>
         <v/>
       </c>
@@ -679,7 +1041,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Each grant: over or under budget to 30 September 2026</t>
         </is>
@@ -711,11 +1073,11 @@
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="11">
         <f>Workings!B50</f>
         <v/>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="9">
         <f>Workings!B49</f>
         <v/>
       </c>
@@ -726,11 +1088,11 @@
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="11">
         <f>Workings!B82</f>
         <v/>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="9">
         <f>Workings!B81</f>
         <v/>
       </c>
@@ -741,11 +1103,11 @@
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="11">
         <f>Workings!B108</f>
         <v/>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="9">
         <f>Workings!B107</f>
         <v/>
       </c>
@@ -756,11 +1118,11 @@
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="11">
         <f>Workings!B131</f>
         <v/>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="9">
         <f>Workings!B130</f>
         <v/>
       </c>
@@ -771,11 +1133,11 @@
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="11">
         <f>Workings!B160</f>
         <v/>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="9">
         <f>Workings!B159</f>
         <v/>
       </c>
@@ -786,27 +1148,44 @@
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="11">
         <f>Workings!B180</f>
         <v/>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="9">
         <f>Workings!B179</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -835,14 +1214,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -869,511 +1248,727 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Youth outreach grant</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="9" t="n">
         <v>22800</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="9" t="n">
         <v>21500</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="14">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Housing support grant</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="9" t="n">
         <v>31200</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="9" t="n">
         <v>30500</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Community meals grant</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="9" t="n">
         <v>4300</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="9" t="n">
         <v>4100</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="14">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Digital literacy grant</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="9" t="n">
         <v>4900</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="9" t="n">
         <v>5200</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="14">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Mental health first aid grant</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="9" t="n">
         <v>10800</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="9" t="n">
         <v>9400</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="14">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Volunteer coordinator grant</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="9" t="n">
         <v>27900</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="9" t="n">
         <v>18400</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="14">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="9" t="n">
         <v>41600</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="14">
         <f>B13-C13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Program fees</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="9" t="n">
         <v>28300</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="9" t="n">
         <v>26800</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="14">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
         <v>1380</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="9" t="n">
         <v>1450</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="14">
         <f>B15-C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="16">
         <f>SUM(B6:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="16">
         <f>SUM(C6:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="17">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Grant-funded program wages</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="9" t="n">
         <v>-57750</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="9" t="n">
         <v>-55275</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="14">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Grant-funded program costs</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="9" t="n">
         <v>-19250</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="9" t="n">
         <v>-18425</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="14">
         <f>B19-C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Program delivery wages (untied)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="9" t="n">
         <v>-14500</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="9" t="n">
         <v>-14000</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="14">
         <f>B20-C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Program costs (untied)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="9" t="n">
         <v>-6100</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="9" t="n">
         <v>-5500</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="14">
         <f>B21-C21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Total program spend</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="16">
         <f>SUM(B18:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="16">
         <f>SUM(C18:C21)</f>
         <v/>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="17">
         <f>B22-C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Fundraising</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Grant writing and reporting</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="9" t="n">
         <v>-7100</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="9" t="n">
         <v>-7100</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="14">
         <f>B24-C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Donor campaigns</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="9" t="n">
         <v>-5400</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="9" t="n">
         <v>-2200</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="14">
         <f>B25-C25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Event costs</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="9" t="n">
         <v>-16900</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="9" t="n">
         <v>-2400</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="14">
         <f>B26-C26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Total fundraising costs</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="16">
         <f>SUM(B24:B26)</f>
         <v/>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="16">
         <f>SUM(C24:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="17">
         <f>B27-C27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Administration wages</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="9" t="n">
         <v>-18300</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="9" t="n">
         <v>-18300</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="14">
         <f>B29-C29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="9" t="n">
         <v>-10000</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="9" t="n">
         <v>-10000</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="14">
         <f>B30-C30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Other administration</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="9" t="n">
         <v>-7600</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="9" t="n">
         <v>-8000</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="14">
         <f>B31-C31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Total administration</t>
         </is>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="16">
         <f>SUM(B29:B31)</f>
         <v/>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="16">
         <f>SUM(C29:C31)</f>
         <v/>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="17">
         <f>B32-C32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="16" t="n">
         <v>-2900</v>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="16" t="n">
         <v>-2900</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="17">
         <f>B33-C33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="16">
         <f>B22+B27+B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="16">
         <f>C22+C27+C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="17">
         <f>B34-C34</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Surplus for the month</t>
         </is>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="19">
         <f>B16+B34</f>
         <v/>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="19">
         <f>C16+C34</f>
         <v/>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="20">
         <f>B35-C35</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" priority="25" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="cellIs" priority="27" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
+    <cfRule type="cellIs" priority="29" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
+    <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24">
+    <cfRule type="cellIs" priority="33" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25">
+    <cfRule type="cellIs" priority="35" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26">
+    <cfRule type="cellIs" priority="37" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="38" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27">
+    <cfRule type="cellIs" priority="39" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="40" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29">
+    <cfRule type="cellIs" priority="41" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30">
+    <cfRule type="cellIs" priority="43" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="44" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D31">
+    <cfRule type="cellIs" priority="45" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="46" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D32">
+    <cfRule type="cellIs" priority="47" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="48" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33">
+    <cfRule type="cellIs" priority="49" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="50" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34">
+    <cfRule type="cellIs" priority="51" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="52" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D35">
+    <cfRule type="cellIs" priority="53" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="54" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1410,14 +2005,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1444,251 +2039,251 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Current assets</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="9" t="n">
         <v>480780</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="9" t="n">
         <v>525675</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="14">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Program fees receivable</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="9" t="n">
         <v>10400</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="9" t="n">
         <v>9800</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Grants receivable (spent ahead of instalment)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="9" t="n">
         <v>20900</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="9" t="n">
         <v>9700</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="14">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Prepayments</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="9" t="n">
         <v>21000</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="9" t="n">
         <v>21000</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="14">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="16">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="16">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="17">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Vehicles and equipment</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="16" t="n">
         <v>172200</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="16" t="n">
         <v>175100</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="17">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="16">
         <f>B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="16">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="17">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Current liabilities</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Payables (bills due next month)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="9" t="n">
         <v>65250</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="9" t="n">
         <v>46525</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="14">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Grants received in advance (unspent)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
         <v>156100</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="9" t="n">
         <v>221900</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="14">
         <f>B15-C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Employee leave provisions</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="9" t="n">
         <v>166600</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="9" t="n">
         <v>165900</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="14">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="16">
         <f>SUM(B14:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="16">
         <f>SUM(C14:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="17">
         <f>B17-C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Net assets</t>
         </is>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="19">
         <f>B12-B17</f>
         <v/>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="19">
         <f>C12-C17</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Accumulated funds</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="19" t="n">
         <v>317330</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="19" t="n">
         <v>306950</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="20">
         <f>B20-C20</f>
         <v/>
       </c>
@@ -1699,7 +2294,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1733,14 +2328,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1767,238 +2362,334 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Operating activities</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Grant instalments received</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="14">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Donations and fundraising received</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="9" t="n">
         <v>69500</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="9" t="n">
         <v>18400</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Program fees received</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="9" t="n">
         <v>27700</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="9" t="n">
         <v>26100</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="14">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Interest received</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="9" t="n">
         <v>1380</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="9" t="n">
         <v>1450</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="14">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Payments to suppliers</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="9" t="n">
         <v>-46525</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="9" t="n">
         <v>-36500</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="14">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Payments to employees</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="9" t="n">
         <v>-96950</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="9" t="n">
         <v>-93775</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="16">
         <f>SUM(B6:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="16">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="17">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Investing activities</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Purchase of vehicles and equipment</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="14">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Net cash from investing activities</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="16">
         <f>SUM(B14:B14)</f>
         <v/>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="16">
         <f>SUM(C14:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="17">
         <f>B15-C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="16">
         <f>B12+B15</f>
         <v/>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="16">
         <f>C12+C15</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="17">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Cash at start of month</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="16" t="n">
         <v>525675</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="16" t="n">
         <v>610000</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="17">
         <f>B17-C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Cash at end of month</t>
         </is>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="19">
         <f>B17+B16</f>
         <v/>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="19">
         <f>C17+C16</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2041,14 +2732,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -2128,335 +2819,338 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>State Department of Families</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="22" t="n">
         <v>480000</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="23" t="n">
         <v>45839</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="23" t="n">
         <v>46568</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="22" t="n">
         <v>300000</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="22" t="n">
         <v>306300</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="22" t="n">
         <v>21500</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="22" t="n">
         <v>22800</v>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="22" t="n">
         <v>300000</v>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="24">
         <f>IF(J7=0,"",G7/J7)</f>
         <v/>
       </c>
-      <c r="L7" s="20">
+      <c r="L7" s="22">
         <f>C7-G7</f>
         <v/>
       </c>
-      <c r="M7" s="20" t="n">
+      <c r="M7" s="22" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>State Housing Program</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="22" t="n">
         <v>360000</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="23" t="n">
         <v>46023</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="23" t="n">
         <v>46387</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="22" t="n">
         <v>360000</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="22" t="n">
         <v>257700</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="22" t="n">
         <v>30500</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="22" t="n">
         <v>31200</v>
       </c>
-      <c r="J8" s="20" t="n">
+      <c r="J8" s="22" t="n">
         <v>270000</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="24">
         <f>IF(J8=0,"",G8/J8)</f>
         <v/>
       </c>
-      <c r="L8" s="20">
+      <c r="L8" s="22">
         <f>C8-G8</f>
         <v/>
       </c>
-      <c r="M8" s="20" t="n">
+      <c r="M8" s="22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Federal health program</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>120000</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="23" t="n">
         <v>46477</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="22" t="n">
         <v>57200</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="22" t="n">
         <v>9400</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="22" t="n">
         <v>10800</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="24">
         <f>IF(J9=0,"",G9/J9)</f>
         <v/>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="22">
         <f>C9-G9</f>
         <v/>
       </c>
-      <c r="M9" s="20" t="n">
+      <c r="M9" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Philanthropic foundation</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>90000</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="23" t="n">
         <v>45931</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="23" t="n">
         <v>46477</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="22" t="n">
         <v>45000</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="22" t="n">
         <v>59600</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="22" t="n">
         <v>5200</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="22" t="n">
         <v>4900</v>
       </c>
-      <c r="J10" s="20" t="n">
+      <c r="J10" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="24">
         <f>IF(J10=0,"",G10/J10)</f>
         <v/>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="22">
         <f>C10-G10</f>
         <v/>
       </c>
-      <c r="M10" s="20" t="n">
+      <c r="M10" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Local council community grant</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="22" t="n">
         <v>48000</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="23" t="n">
         <v>46204</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="23" t="n">
         <v>46568</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="22" t="n">
         <v>48000</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="22" t="n">
         <v>4100</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="22" t="n">
         <v>4300</v>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="24">
         <f>IF(J11=0,"",G11/J11)</f>
         <v/>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="22">
         <f>C11-G11</f>
         <v/>
       </c>
-      <c r="M11" s="20" t="n">
+      <c r="M11" s="22" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>State volunteering grant</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="22" t="n">
         <v>36000</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="23" t="n">
         <v>46082</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="23" t="n">
         <v>46446</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="22" t="n">
         <v>36000</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="22" t="n">
         <v>21000</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="22" t="n">
         <v>21000</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="24">
         <f>IF(J12=0,"",G12/J12)</f>
         <v/>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="22">
         <f>C12-G12</f>
         <v/>
       </c>
-      <c r="M12" s="20" t="n">
+      <c r="M12" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="26">
         <f>SUM(C7:C12)</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <f>SUM(F7:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <f>SUM(G7:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="26">
         <f>SUM(H7:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="26">
         <f>SUM(I7:I12)</f>
         <v/>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="26">
         <f>SUM(J7:J12)</f>
         <v/>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="26">
         <f>SUM(L7:L12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:M12"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2485,27 +3179,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Cost to raise a dollar</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Fundraising costs ÷ money raised (grants, donations, events), in cents</t>
         </is>
@@ -2530,10 +3224,10 @@
           <t>Grant writing and reporting</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="22" t="n">
         <v>7100</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="22" t="n">
         <v>7100</v>
       </c>
     </row>
@@ -2543,10 +3237,10 @@
           <t>Donor campaigns</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="22" t="n">
         <v>5400</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>2200</v>
       </c>
     </row>
@@ -2556,10 +3250,10 @@
           <t>Event costs</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="22" t="n">
         <v>16900</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -2569,11 +3263,11 @@
           <t>Fundraising costs</t>
         </is>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="22">
         <f>B8+B9+B10</f>
         <v/>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="22">
         <f>C8+C9+C10</f>
         <v/>
       </c>
@@ -2584,10 +3278,10 @@
           <t>Grant income</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="22" t="n">
         <v>77000</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="22" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -2597,10 +3291,10 @@
           <t>Donations</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="22" t="n">
         <v>27900</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="22" t="n">
         <v>18400</v>
       </c>
     </row>
@@ -2610,10 +3304,10 @@
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="22" t="n">
         <v>41600</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2623,26 +3317,26 @@
           <t>Money raised</t>
         </is>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="22">
         <f>B12+B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="22">
         <f>C12+C13+C14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Cost per dollar raised</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="30">
         <f>B11/B15*100</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="30">
         <f>C11/C15*100</f>
         <v/>
       </c>
@@ -2657,14 +3351,14 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Unrestricted cash runway</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>(Cash at bank − unspent grant money) ÷ this month's cash spending</t>
         </is>
@@ -2689,10 +3383,10 @@
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="22" t="n">
         <v>480780</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="22" t="n">
         <v>525675</v>
       </c>
     </row>
@@ -2702,10 +3396,10 @@
           <t>Less unspent grant money (belongs to funders' programs)</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="22" t="n">
         <v>-156100</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="22" t="n">
         <v>-221900</v>
       </c>
     </row>
@@ -2715,11 +3409,11 @@
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="22">
         <f>B23+B24</f>
         <v/>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="22">
         <f>C23+C24</f>
         <v/>
       </c>
@@ -2730,24 +3424,24 @@
           <t>Cash spending in the month (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="22" t="n">
         <v>162900</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="22" t="n">
         <v>141200</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="31">
         <f>B25/B26</f>
         <v/>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="31">
         <f>C25/C26</f>
         <v/>
       </c>
@@ -2762,14 +3456,14 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Grants ending in the next 6 months</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>Grant total − spent to date, for each grant ending soon</t>
         </is>
@@ -2789,7 +3483,7 @@
           <t>Housing support (ends 31 Dec 2026)</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
+      <c r="B34" s="22" t="n">
         <v>102300</v>
       </c>
     </row>
@@ -2799,17 +3493,17 @@
           <t>Volunteer coordinator (ends 28 Feb 2027)</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="22" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>Total still to spend</t>
         </is>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="32">
         <f>B34+B35</f>
         <v/>
       </c>
@@ -2824,14 +3518,14 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>State Department of Families · $480,000 · Jul 2025 to Jun 2027</t>
         </is>
@@ -2851,7 +3545,7 @@
           <t>Grant total</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n">
+      <c r="B43" s="22" t="n">
         <v>480000</v>
       </c>
     </row>
@@ -2861,7 +3555,7 @@
           <t>Received from the funder</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="22" t="n">
         <v>300000</v>
       </c>
     </row>
@@ -2871,7 +3565,7 @@
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
+      <c r="B45" s="22" t="n">
         <v>306300</v>
       </c>
     </row>
@@ -2881,7 +3575,7 @@
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n">
+      <c r="B46" s="22" t="n">
         <v>300000</v>
       </c>
     </row>
@@ -2891,7 +3585,7 @@
           <t>Months left</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n">
+      <c r="B47" s="22" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2901,7 +3595,7 @@
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="22">
         <f>B43-B45</f>
         <v/>
       </c>
@@ -2912,25 +3606,25 @@
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="22">
         <f>B45-B46</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="33">
         <f>B45/B46-1</f>
         <v/>
       </c>
     </row>
     <row r="51"/>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
@@ -2964,13 +3658,13 @@
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B54" s="9" t="n">
         <v>17363</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="11">
         <f>IF(C54=0,"",B54/C54)</f>
         <v/>
       </c>
@@ -2981,13 +3675,13 @@
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n">
+      <c r="B55" s="9" t="n">
         <v>21144</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="11">
         <f>IF(C55=0,"",B55/C55)</f>
         <v/>
       </c>
@@ -2998,13 +3692,13 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="9" t="n">
         <v>17537</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="11">
         <f>IF(C56=0,"",B56/C56)</f>
         <v/>
       </c>
@@ -3015,13 +3709,13 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="9" t="n">
         <v>21925</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="11">
         <f>IF(C57=0,"",B57/C57)</f>
         <v/>
       </c>
@@ -3032,13 +3726,13 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="9" t="n">
         <v>21079</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="11">
         <f>IF(C58=0,"",B58/C58)</f>
         <v/>
       </c>
@@ -3049,13 +3743,13 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n">
+      <c r="B59" s="9" t="n">
         <v>19272</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="11">
         <f>IF(C59=0,"",B59/C59)</f>
         <v/>
       </c>
@@ -3066,13 +3760,13 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B60" s="7" t="n">
+      <c r="B60" s="9" t="n">
         <v>21157</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="11">
         <f>IF(C60=0,"",B60/C60)</f>
         <v/>
       </c>
@@ -3083,13 +3777,13 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B61" s="7" t="n">
+      <c r="B61" s="9" t="n">
         <v>20743</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="11">
         <f>IF(C61=0,"",B61/C61)</f>
         <v/>
       </c>
@@ -3100,13 +3794,13 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B62" s="7" t="n">
+      <c r="B62" s="9" t="n">
         <v>16515</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="11">
         <f>IF(C62=0,"",B62/C62)</f>
         <v/>
       </c>
@@ -3117,13 +3811,13 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B63" s="9" t="n">
         <v>20451</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="11">
         <f>IF(C63=0,"",B63/C63)</f>
         <v/>
       </c>
@@ -3134,13 +3828,13 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="B64" s="7" t="n">
+      <c r="B64" s="9" t="n">
         <v>21174</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="11">
         <f>IF(C64=0,"",B64/C64)</f>
         <v/>
       </c>
@@ -3151,13 +3845,13 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B65" s="7" t="n">
+      <c r="B65" s="9" t="n">
         <v>20366</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="11">
         <f>IF(C65=0,"",B65/C65)</f>
         <v/>
       </c>
@@ -3168,13 +3862,13 @@
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n">
+      <c r="B66" s="9" t="n">
         <v>23274</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="11">
         <f>IF(C66=0,"",B66/C66)</f>
         <v/>
       </c>
@@ -3185,13 +3879,13 @@
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B67" s="9" t="n">
         <v>21500</v>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="11">
         <f>IF(C67=0,"",B67/C67)</f>
         <v/>
       </c>
@@ -3202,32 +3896,32 @@
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
+      <c r="B68" s="9" t="n">
         <v>22800</v>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="11">
         <f>IF(C68=0,"",B68/C68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="23" t="inlineStr">
+      <c r="A69" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="34">
         <f>SUM(B54:B68)</f>
         <v/>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="34">
         <f>SUM(C54:C68)</f>
         <v/>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="35">
         <f>IF(C69=0,"",B69/C69)</f>
         <v/>
       </c>
@@ -3235,14 +3929,14 @@
     <row r="70"/>
     <row r="71"/>
     <row r="72">
-      <c r="A72" s="25" t="inlineStr">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="26" t="inlineStr">
+      <c r="A73" s="28" t="inlineStr">
         <is>
           <t>State Housing Program · $360,000 · Jan 2026 to Dec 2026</t>
         </is>
@@ -3262,7 +3956,7 @@
           <t>Grant total</t>
         </is>
       </c>
-      <c r="B75" s="20" t="n">
+      <c r="B75" s="22" t="n">
         <v>360000</v>
       </c>
     </row>
@@ -3272,7 +3966,7 @@
           <t>Received from the funder</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n">
+      <c r="B76" s="22" t="n">
         <v>360000</v>
       </c>
     </row>
@@ -3282,7 +3976,7 @@
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="B77" s="20" t="n">
+      <c r="B77" s="22" t="n">
         <v>257700</v>
       </c>
     </row>
@@ -3292,7 +3986,7 @@
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n">
+      <c r="B78" s="22" t="n">
         <v>270000</v>
       </c>
     </row>
@@ -3302,7 +3996,7 @@
           <t>Months left</t>
         </is>
       </c>
-      <c r="B79" s="20" t="n">
+      <c r="B79" s="22" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3312,7 +4006,7 @@
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B80" s="20">
+      <c r="B80" s="22">
         <f>B75-B77</f>
         <v/>
       </c>
@@ -3323,25 +4017,25 @@
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B81" s="20">
+      <c r="B81" s="22">
         <f>B77-B78</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="27" t="inlineStr">
+      <c r="A82" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B82" s="31">
+      <c r="B82" s="33">
         <f>B77/B78-1</f>
         <v/>
       </c>
     </row>
     <row r="83"/>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
@@ -3375,13 +4069,13 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B86" s="7" t="n">
+      <c r="B86" s="9" t="n">
         <v>30502</v>
       </c>
-      <c r="C86" s="7" t="n">
+      <c r="C86" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="11">
         <f>IF(C86=0,"",B86/C86)</f>
         <v/>
       </c>
@@ -3392,13 +4086,13 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B87" s="7" t="n">
+      <c r="B87" s="9" t="n">
         <v>26508</v>
       </c>
-      <c r="C87" s="7" t="n">
+      <c r="C87" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="11">
         <f>IF(C87=0,"",B87/C87)</f>
         <v/>
       </c>
@@ -3409,13 +4103,13 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B88" s="7" t="n">
+      <c r="B88" s="9" t="n">
         <v>24832</v>
       </c>
-      <c r="C88" s="7" t="n">
+      <c r="C88" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="11">
         <f>IF(C88=0,"",B88/C88)</f>
         <v/>
       </c>
@@ -3426,13 +4120,13 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B89" s="7" t="n">
+      <c r="B89" s="9" t="n">
         <v>23730</v>
       </c>
-      <c r="C89" s="7" t="n">
+      <c r="C89" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="11">
         <f>IF(C89=0,"",B89/C89)</f>
         <v/>
       </c>
@@ -3443,13 +4137,13 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="B90" s="7" t="n">
+      <c r="B90" s="9" t="n">
         <v>31337</v>
       </c>
-      <c r="C90" s="7" t="n">
+      <c r="C90" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="11">
         <f>IF(C90=0,"",B90/C90)</f>
         <v/>
       </c>
@@ -3460,13 +4154,13 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B91" s="7" t="n">
+      <c r="B91" s="9" t="n">
         <v>29994</v>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="11">
         <f>IF(C91=0,"",B91/C91)</f>
         <v/>
       </c>
@@ -3477,13 +4171,13 @@
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B92" s="7" t="n">
+      <c r="B92" s="9" t="n">
         <v>29097</v>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="11">
         <f>IF(C92=0,"",B92/C92)</f>
         <v/>
       </c>
@@ -3494,13 +4188,13 @@
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B93" s="7" t="n">
+      <c r="B93" s="9" t="n">
         <v>30500</v>
       </c>
-      <c r="C93" s="7" t="n">
+      <c r="C93" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="11">
         <f>IF(C93=0,"",B93/C93)</f>
         <v/>
       </c>
@@ -3511,32 +4205,32 @@
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B94" s="7" t="n">
+      <c r="B94" s="9" t="n">
         <v>31200</v>
       </c>
-      <c r="C94" s="7" t="n">
+      <c r="C94" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="11">
         <f>IF(C94=0,"",B94/C94)</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="23" t="inlineStr">
+      <c r="A95" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B95" s="32">
+      <c r="B95" s="34">
         <f>SUM(B86:B94)</f>
         <v/>
       </c>
-      <c r="C95" s="32">
+      <c r="C95" s="34">
         <f>SUM(C86:C94)</f>
         <v/>
       </c>
-      <c r="D95" s="33">
+      <c r="D95" s="35">
         <f>IF(C95=0,"",B95/C95)</f>
         <v/>
       </c>
@@ -3544,14 +4238,14 @@
     <row r="96"/>
     <row r="97"/>
     <row r="98">
-      <c r="A98" s="25" t="inlineStr">
+      <c r="A98" s="27" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="A99" s="28" t="inlineStr">
         <is>
           <t>Federal health program · $120,000 · Apr 2026 to Mar 2027</t>
         </is>
@@ -3571,7 +4265,7 @@
           <t>Grant total</t>
         </is>
       </c>
-      <c r="B101" s="20" t="n">
+      <c r="B101" s="22" t="n">
         <v>120000</v>
       </c>
     </row>
@@ -3581,7 +4275,7 @@
           <t>Received from the funder</t>
         </is>
       </c>
-      <c r="B102" s="20" t="n">
+      <c r="B102" s="22" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -3591,7 +4285,7 @@
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="B103" s="20" t="n">
+      <c r="B103" s="22" t="n">
         <v>57200</v>
       </c>
     </row>
@@ -3601,7 +4295,7 @@
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="B104" s="20" t="n">
+      <c r="B104" s="22" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -3611,7 +4305,7 @@
           <t>Months left</t>
         </is>
       </c>
-      <c r="B105" s="20" t="n">
+      <c r="B105" s="22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3621,7 +4315,7 @@
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B106" s="20">
+      <c r="B106" s="22">
         <f>B101-B103</f>
         <v/>
       </c>
@@ -3632,25 +4326,25 @@
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B107" s="20">
+      <c r="B107" s="22">
         <f>B103-B104</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="27" t="inlineStr">
+      <c r="A108" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B108" s="31">
+      <c r="B108" s="33">
         <f>B103/B104-1</f>
         <v/>
       </c>
     </row>
     <row r="109"/>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
@@ -3684,13 +4378,13 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B112" s="7" t="n">
+      <c r="B112" s="9" t="n">
         <v>9584</v>
       </c>
-      <c r="C112" s="7" t="n">
+      <c r="C112" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="11">
         <f>IF(C112=0,"",B112/C112)</f>
         <v/>
       </c>
@@ -3701,13 +4395,13 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="B113" s="7" t="n">
+      <c r="B113" s="9" t="n">
         <v>8950</v>
       </c>
-      <c r="C113" s="7" t="n">
+      <c r="C113" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="D113" s="9">
+      <c r="D113" s="11">
         <f>IF(C113=0,"",B113/C113)</f>
         <v/>
       </c>
@@ -3718,13 +4412,13 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B114" s="7" t="n">
+      <c r="B114" s="9" t="n">
         <v>9797</v>
       </c>
-      <c r="C114" s="7" t="n">
+      <c r="C114" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="11">
         <f>IF(C114=0,"",B114/C114)</f>
         <v/>
       </c>
@@ -3735,13 +4429,13 @@
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B115" s="7" t="n">
+      <c r="B115" s="9" t="n">
         <v>8669</v>
       </c>
-      <c r="C115" s="7" t="n">
+      <c r="C115" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="D115" s="9">
+      <c r="D115" s="11">
         <f>IF(C115=0,"",B115/C115)</f>
         <v/>
       </c>
@@ -3752,13 +4446,13 @@
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B116" s="7" t="n">
+      <c r="B116" s="9" t="n">
         <v>9400</v>
       </c>
-      <c r="C116" s="7" t="n">
+      <c r="C116" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="11">
         <f>IF(C116=0,"",B116/C116)</f>
         <v/>
       </c>
@@ -3769,32 +4463,32 @@
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B117" s="7" t="n">
+      <c r="B117" s="9" t="n">
         <v>10800</v>
       </c>
-      <c r="C117" s="7" t="n">
+      <c r="C117" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="D117" s="9">
+      <c r="D117" s="11">
         <f>IF(C117=0,"",B117/C117)</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="23" t="inlineStr">
+      <c r="A118" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B118" s="32">
+      <c r="B118" s="34">
         <f>SUM(B112:B117)</f>
         <v/>
       </c>
-      <c r="C118" s="32">
+      <c r="C118" s="34">
         <f>SUM(C112:C117)</f>
         <v/>
       </c>
-      <c r="D118" s="33">
+      <c r="D118" s="35">
         <f>IF(C118=0,"",B118/C118)</f>
         <v/>
       </c>
@@ -3802,14 +4496,14 @@
     <row r="119"/>
     <row r="120"/>
     <row r="121">
-      <c r="A121" s="25" t="inlineStr">
+      <c r="A121" s="27" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="26" t="inlineStr">
+      <c r="A122" s="28" t="inlineStr">
         <is>
           <t>Philanthropic foundation · $90,000 · Oct 2025 to Mar 2027</t>
         </is>
@@ -3829,7 +4523,7 @@
           <t>Grant total</t>
         </is>
       </c>
-      <c r="B124" s="20" t="n">
+      <c r="B124" s="22" t="n">
         <v>90000</v>
       </c>
     </row>
@@ -3839,7 +4533,7 @@
           <t>Received from the funder</t>
         </is>
       </c>
-      <c r="B125" s="20" t="n">
+      <c r="B125" s="22" t="n">
         <v>45000</v>
       </c>
     </row>
@@ -3849,7 +4543,7 @@
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="B126" s="20" t="n">
+      <c r="B126" s="22" t="n">
         <v>59600</v>
       </c>
     </row>
@@ -3859,7 +4553,7 @@
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="B127" s="20" t="n">
+      <c r="B127" s="22" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -3869,7 +4563,7 @@
           <t>Months left</t>
         </is>
       </c>
-      <c r="B128" s="20" t="n">
+      <c r="B128" s="22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3879,7 +4573,7 @@
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B129" s="20">
+      <c r="B129" s="22">
         <f>B124-B126</f>
         <v/>
       </c>
@@ -3890,25 +4584,25 @@
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B130" s="20">
+      <c r="B130" s="22">
         <f>B126-B127</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="27" t="inlineStr">
+      <c r="A131" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B131" s="31">
+      <c r="B131" s="33">
         <f>B126/B127-1</f>
         <v/>
       </c>
     </row>
     <row r="132"/>
     <row r="133">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
@@ -3942,13 +4636,13 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B135" s="7" t="n">
+      <c r="B135" s="9" t="n">
         <v>5160</v>
       </c>
-      <c r="C135" s="7" t="n">
+      <c r="C135" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D135" s="9">
+      <c r="D135" s="11">
         <f>IF(C135=0,"",B135/C135)</f>
         <v/>
       </c>
@@ -3959,13 +4653,13 @@
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B136" s="7" t="n">
+      <c r="B136" s="9" t="n">
         <v>4585</v>
       </c>
-      <c r="C136" s="7" t="n">
+      <c r="C136" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="11">
         <f>IF(C136=0,"",B136/C136)</f>
         <v/>
       </c>
@@ -3976,13 +4670,13 @@
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B137" s="7" t="n">
+      <c r="B137" s="9" t="n">
         <v>5221</v>
       </c>
-      <c r="C137" s="7" t="n">
+      <c r="C137" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D137" s="9">
+      <c r="D137" s="11">
         <f>IF(C137=0,"",B137/C137)</f>
         <v/>
       </c>
@@ -3993,13 +4687,13 @@
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B138" s="7" t="n">
+      <c r="B138" s="9" t="n">
         <v>4426</v>
       </c>
-      <c r="C138" s="7" t="n">
+      <c r="C138" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="11">
         <f>IF(C138=0,"",B138/C138)</f>
         <v/>
       </c>
@@ -4010,13 +4704,13 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B139" s="7" t="n">
+      <c r="B139" s="9" t="n">
         <v>5408</v>
       </c>
-      <c r="C139" s="7" t="n">
+      <c r="C139" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D139" s="9">
+      <c r="D139" s="11">
         <f>IF(C139=0,"",B139/C139)</f>
         <v/>
       </c>
@@ -4027,13 +4721,13 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B140" s="7" t="n">
+      <c r="B140" s="9" t="n">
         <v>5427</v>
       </c>
-      <c r="C140" s="7" t="n">
+      <c r="C140" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="11">
         <f>IF(C140=0,"",B140/C140)</f>
         <v/>
       </c>
@@ -4044,13 +4738,13 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B141" s="7" t="n">
+      <c r="B141" s="9" t="n">
         <v>5509</v>
       </c>
-      <c r="C141" s="7" t="n">
+      <c r="C141" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D141" s="11">
         <f>IF(C141=0,"",B141/C141)</f>
         <v/>
       </c>
@@ -4061,13 +4755,13 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="B142" s="7" t="n">
+      <c r="B142" s="9" t="n">
         <v>4635</v>
       </c>
-      <c r="C142" s="7" t="n">
+      <c r="C142" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="11">
         <f>IF(C142=0,"",B142/C142)</f>
         <v/>
       </c>
@@ -4078,13 +4772,13 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B143" s="7" t="n">
+      <c r="B143" s="9" t="n">
         <v>4316</v>
       </c>
-      <c r="C143" s="7" t="n">
+      <c r="C143" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D143" s="9">
+      <c r="D143" s="11">
         <f>IF(C143=0,"",B143/C143)</f>
         <v/>
       </c>
@@ -4095,13 +4789,13 @@
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B144" s="7" t="n">
+      <c r="B144" s="9" t="n">
         <v>4813</v>
       </c>
-      <c r="C144" s="7" t="n">
+      <c r="C144" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="11">
         <f>IF(C144=0,"",B144/C144)</f>
         <v/>
       </c>
@@ -4112,13 +4806,13 @@
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B145" s="7" t="n">
+      <c r="B145" s="9" t="n">
         <v>5200</v>
       </c>
-      <c r="C145" s="7" t="n">
+      <c r="C145" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D145" s="11">
         <f>IF(C145=0,"",B145/C145)</f>
         <v/>
       </c>
@@ -4129,32 +4823,32 @@
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B146" s="7" t="n">
+      <c r="B146" s="9" t="n">
         <v>4900</v>
       </c>
-      <c r="C146" s="7" t="n">
+      <c r="C146" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="11">
         <f>IF(C146=0,"",B146/C146)</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="23" t="inlineStr">
+      <c r="A147" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B147" s="32">
+      <c r="B147" s="34">
         <f>SUM(B135:B146)</f>
         <v/>
       </c>
-      <c r="C147" s="32">
+      <c r="C147" s="34">
         <f>SUM(C135:C146)</f>
         <v/>
       </c>
-      <c r="D147" s="33">
+      <c r="D147" s="35">
         <f>IF(C147=0,"",B147/C147)</f>
         <v/>
       </c>
@@ -4162,14 +4856,14 @@
     <row r="148"/>
     <row r="149"/>
     <row r="150">
-      <c r="A150" s="25" t="inlineStr">
+      <c r="A150" s="27" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="26" t="inlineStr">
+      <c r="A151" s="28" t="inlineStr">
         <is>
           <t>Local council community grant · $48,000 · Jul 2026 to Jun 2027</t>
         </is>
@@ -4189,7 +4883,7 @@
           <t>Grant total</t>
         </is>
       </c>
-      <c r="B153" s="20" t="n">
+      <c r="B153" s="22" t="n">
         <v>48000</v>
       </c>
     </row>
@@ -4199,7 +4893,7 @@
           <t>Received from the funder</t>
         </is>
       </c>
-      <c r="B154" s="20" t="n">
+      <c r="B154" s="22" t="n">
         <v>48000</v>
       </c>
     </row>
@@ -4209,7 +4903,7 @@
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="B155" s="20" t="n">
+      <c r="B155" s="22" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -4219,7 +4913,7 @@
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="B156" s="20" t="n">
+      <c r="B156" s="22" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -4229,7 +4923,7 @@
           <t>Months left</t>
         </is>
       </c>
-      <c r="B157" s="20" t="n">
+      <c r="B157" s="22" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4239,7 +4933,7 @@
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B158" s="20">
+      <c r="B158" s="22">
         <f>B153-B155</f>
         <v/>
       </c>
@@ -4250,25 +4944,25 @@
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B159" s="20">
+      <c r="B159" s="22">
         <f>B155-B156</f>
         <v/>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="27" t="inlineStr">
+      <c r="A160" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B160" s="31">
+      <c r="B160" s="33">
         <f>B155/B156-1</f>
         <v/>
       </c>
     </row>
     <row r="161"/>
     <row r="162">
-      <c r="A162" s="8" t="inlineStr">
+      <c r="A162" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
@@ -4302,13 +4996,13 @@
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B164" s="7" t="n">
+      <c r="B164" s="9" t="n">
         <v>3600</v>
       </c>
-      <c r="C164" s="7" t="n">
+      <c r="C164" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D164" s="9">
+      <c r="D164" s="11">
         <f>IF(C164=0,"",B164/C164)</f>
         <v/>
       </c>
@@ -4319,13 +5013,13 @@
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B165" s="7" t="n">
+      <c r="B165" s="9" t="n">
         <v>4100</v>
       </c>
-      <c r="C165" s="7" t="n">
+      <c r="C165" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D165" s="9">
+      <c r="D165" s="11">
         <f>IF(C165=0,"",B165/C165)</f>
         <v/>
       </c>
@@ -4336,32 +5030,32 @@
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B166" s="7" t="n">
+      <c r="B166" s="9" t="n">
         <v>4300</v>
       </c>
-      <c r="C166" s="7" t="n">
+      <c r="C166" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D166" s="9">
+      <c r="D166" s="11">
         <f>IF(C166=0,"",B166/C166)</f>
         <v/>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="23" t="inlineStr">
+      <c r="A167" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B167" s="32">
+      <c r="B167" s="34">
         <f>SUM(B164:B166)</f>
         <v/>
       </c>
-      <c r="C167" s="32">
+      <c r="C167" s="34">
         <f>SUM(C164:C166)</f>
         <v/>
       </c>
-      <c r="D167" s="33">
+      <c r="D167" s="35">
         <f>IF(C167=0,"",B167/C167)</f>
         <v/>
       </c>
@@ -4369,14 +5063,14 @@
     <row r="168"/>
     <row r="169"/>
     <row r="170">
-      <c r="A170" s="25" t="inlineStr">
+      <c r="A170" s="27" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="26" t="inlineStr">
+      <c r="A171" s="28" t="inlineStr">
         <is>
           <t>State volunteering grant · $36,000 · Mar 2026 to Feb 2027</t>
         </is>
@@ -4396,7 +5090,7 @@
           <t>Grant total</t>
         </is>
       </c>
-      <c r="B173" s="20" t="n">
+      <c r="B173" s="22" t="n">
         <v>36000</v>
       </c>
     </row>
@@ -4406,7 +5100,7 @@
           <t>Received from the funder</t>
         </is>
       </c>
-      <c r="B174" s="20" t="n">
+      <c r="B174" s="22" t="n">
         <v>36000</v>
       </c>
     </row>
@@ -4416,7 +5110,7 @@
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="B175" s="20" t="n">
+      <c r="B175" s="22" t="n">
         <v>21000</v>
       </c>
     </row>
@@ -4426,7 +5120,7 @@
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="B176" s="20" t="n">
+      <c r="B176" s="22" t="n">
         <v>21000</v>
       </c>
     </row>
@@ -4436,7 +5130,7 @@
           <t>Months left</t>
         </is>
       </c>
-      <c r="B177" s="20" t="n">
+      <c r="B177" s="22" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4446,7 +5140,7 @@
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="B178" s="20">
+      <c r="B178" s="22">
         <f>B173-B175</f>
         <v/>
       </c>
@@ -4457,25 +5151,25 @@
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B179" s="20">
+      <c r="B179" s="22">
         <f>B175-B176</f>
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="27" t="inlineStr">
+      <c r="A180" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B180" s="31">
+      <c r="B180" s="33">
         <f>B175/B176-1</f>
         <v/>
       </c>
     </row>
     <row r="181"/>
     <row r="182">
-      <c r="A182" s="8" t="inlineStr">
+      <c r="A182" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
@@ -4509,13 +5203,13 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B184" s="7" t="n">
+      <c r="B184" s="9" t="n">
         <v>2932</v>
       </c>
-      <c r="C184" s="7" t="n">
+      <c r="C184" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D184" s="9">
+      <c r="D184" s="11">
         <f>IF(C184=0,"",B184/C184)</f>
         <v/>
       </c>
@@ -4526,13 +5220,13 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B185" s="7" t="n">
+      <c r="B185" s="9" t="n">
         <v>3555</v>
       </c>
-      <c r="C185" s="7" t="n">
+      <c r="C185" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D185" s="9">
+      <c r="D185" s="11">
         <f>IF(C185=0,"",B185/C185)</f>
         <v/>
       </c>
@@ -4543,13 +5237,13 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="B186" s="7" t="n">
+      <c r="B186" s="9" t="n">
         <v>2649</v>
       </c>
-      <c r="C186" s="7" t="n">
+      <c r="C186" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D186" s="9">
+      <c r="D186" s="11">
         <f>IF(C186=0,"",B186/C186)</f>
         <v/>
       </c>
@@ -4560,13 +5254,13 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B187" s="7" t="n">
+      <c r="B187" s="9" t="n">
         <v>2699</v>
       </c>
-      <c r="C187" s="7" t="n">
+      <c r="C187" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D187" s="9">
+      <c r="D187" s="11">
         <f>IF(C187=0,"",B187/C187)</f>
         <v/>
       </c>
@@ -4577,13 +5271,13 @@
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B188" s="7" t="n">
+      <c r="B188" s="9" t="n">
         <v>3165</v>
       </c>
-      <c r="C188" s="7" t="n">
+      <c r="C188" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D188" s="9">
+      <c r="D188" s="11">
         <f>IF(C188=0,"",B188/C188)</f>
         <v/>
       </c>
@@ -4594,13 +5288,13 @@
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B189" s="7" t="n">
+      <c r="B189" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="C189" s="7" t="n">
+      <c r="C189" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D189" s="9">
+      <c r="D189" s="11">
         <f>IF(C189=0,"",B189/C189)</f>
         <v/>
       </c>
@@ -4611,32 +5305,32 @@
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B190" s="7" t="n">
+      <c r="B190" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="C190" s="7" t="n">
+      <c r="C190" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D190" s="9">
+      <c r="D190" s="11">
         <f>IF(C190=0,"",B190/C190)</f>
         <v/>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="23" t="inlineStr">
+      <c r="A191" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B191" s="32">
+      <c r="B191" s="34">
         <f>SUM(B184:B190)</f>
         <v/>
       </c>
-      <c r="C191" s="32">
+      <c r="C191" s="34">
         <f>SUM(C184:C190)</f>
         <v/>
       </c>
-      <c r="D191" s="33">
+      <c r="D191" s="35">
         <f>IF(C191=0,"",B191/C191)</f>
         <v/>
       </c>
@@ -4650,7 +5344,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4691,56 +5385,56 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>The organisation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>A Brisbane community services charity funded by six grants, donations, events and program fees. About 18 staff. Registered charity, income-tax exempt.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Reporting month</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>September 2026, compared with August 2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Financial year</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>FY2027: 1 July 2026 to 30 June 2027</t>
         </is>
@@ -4748,103 +5442,103 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>State Department of Families: $480,000, 2025-07 to 2027-06</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>State Housing Program: $360,000, 2026-01 to 2026-12</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Local council community grant: $48,000, 2026-07 to 2027-06</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Philanthropic foundation: $90,000, 2025-10 to 2027-03</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Federal health program: $120,000, 2026-04 to 2027-03</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>State volunteering grant: $36,000, 2026-03 to 2027-02</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Grant income</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>recognised as the money is spent on the program</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>Unspent grants</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>instalments received but not yet spent are a liability (grants received in advance)</t>
         </is>
@@ -4852,55 +5546,55 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Other income and costs</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>including the spring appeal in September</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>Fundraising event</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>September gala: income and costs in the same month</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Grant-funded spending</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>75% wages, the rest program costs</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>none: registered charity, income-tax exempt</t>
         </is>
@@ -4908,67 +5602,67 @@
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Cash and balance sheet</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>Suppliers</t>
         </is>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>paid the following month</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>cash at bank less unspent grant money</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>Cash runway</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>unrestricted cash ÷ this month's cash spending</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Reserves target</t>
         </is>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>3 months of spending</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>excluded throughout, for simplicity</t>
         </is>
@@ -4976,7 +5670,7 @@
     </row>
     <row r="32"/>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Checks (all passed)</t>
         </is>
@@ -5024,8 +5718,9 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Print check (done before this file was saved)</t>
         </is>
@@ -5086,7 +5781,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -384,28 +384,14 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="1"/>
+            <idx val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B42318"/>
+                <a:srgbClr val="8A6D3B"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
-                  <a:srgbClr val="B42318"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B42318"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="B42318"/>
+                  <a:srgbClr val="8A6D3B"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -962,7 +948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1036,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Spending to date against budget to date (the grant spread evenly over its months). Over or under budget in red; within 1% in amber.</t>
+          <t>Spending to date against budget to date (the grant spread evenly over its months). Over budget in red, under budget in green; within 1% in amber.</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1165,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1221,7 +1207,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1954,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2012,7 +1998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2280,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2335,7 +2321,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2675,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2739,7 +2725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3127,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3186,7 +3172,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5330,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5392,7 +5378,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5767,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/nfp-sample-statements.xlsx
+++ b/media/exports/nfp-sample-statements.xlsx
@@ -24,13 +24,13 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Income and expenditure'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Income and expenditure'!$A$1:$D$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Balance sheet'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Balance sheet'!$A$1:$D$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cash flow'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cash flow'!$A$1:$D$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Grants'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Grants'!$A$1:$M$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A$1:$D$191</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Assumptions'!$A$1:$B$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A$1:$D$194</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Assumptions'!$A$1:$B$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -948,7 +948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>Workings!B27</f>
+        <f>Workings!B28</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>Workings!C27</f>
+        <f>Workings!C28</f>
         <v/>
       </c>
       <c r="D7" s="8">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>Workings!B36</f>
+        <f>Workings!B39</f>
         <v/>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>Workings!B50</f>
+        <f>Workings!B53</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>Workings!B49</f>
+        <f>Workings!B52</f>
         <v/>
       </c>
     </row>
@@ -1075,11 +1075,11 @@
         </is>
       </c>
       <c r="B15" s="11">
-        <f>Workings!B82</f>
+        <f>Workings!B85</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>Workings!B81</f>
+        <f>Workings!B84</f>
         <v/>
       </c>
     </row>
@@ -1090,11 +1090,11 @@
         </is>
       </c>
       <c r="B16" s="11">
-        <f>Workings!B108</f>
+        <f>Workings!B111</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>Workings!B107</f>
+        <f>Workings!B110</f>
         <v/>
       </c>
     </row>
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="B17" s="11">
-        <f>Workings!B131</f>
+        <f>Workings!B134</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>Workings!B130</f>
+        <f>Workings!B133</f>
         <v/>
       </c>
     </row>
@@ -1120,11 +1120,11 @@
         </is>
       </c>
       <c r="B18" s="11">
-        <f>Workings!B160</f>
+        <f>Workings!B163</f>
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>Workings!B159</f>
+        <f>Workings!B162</f>
         <v/>
       </c>
     </row>
@@ -1135,11 +1135,11 @@
         </is>
       </c>
       <c r="B19" s="11">
-        <f>Workings!B180</f>
+        <f>Workings!B183</f>
         <v/>
       </c>
       <c r="C19" s="9">
-        <f>Workings!B179</f>
+        <f>Workings!B182</f>
         <v/>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1207,7 +1207,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1972,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1998,7 +1998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>480780</v>
+        <v>527060</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>525675</v>
+        <v>547394</v>
       </c>
       <c r="D6" s="14">
         <f>B6-C6</f>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10400</v>
+        <v>11440</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9800</v>
+        <v>10780</v>
       </c>
       <c r="D7" s="14">
         <f>B7-C7</f>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>65250</v>
+        <v>71775</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>46525</v>
+        <v>51178</v>
       </c>
       <c r="D14" s="14">
         <f>B14-C14</f>
@@ -2181,14 +2181,14 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Grants received in advance (unspent)</t>
+          <t>Wages owed (since the last pay run)</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>156100</v>
+        <v>36677</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>221900</v>
+        <v>28711</v>
       </c>
       <c r="D15" s="14">
         <f>B15-C15</f>
@@ -2198,14 +2198,14 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Employee leave provisions</t>
+          <t>Super payable</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>166600</v>
+        <v>4400</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>165900</v>
+        <v>3444</v>
       </c>
       <c r="D16" s="14">
         <f>B16-C16</f>
@@ -2213,64 +2213,132 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>PAYG withholding payable</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>40086</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>26724</v>
+      </c>
+      <c r="D17" s="14">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>GST payable (net)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>25437</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>24972</v>
+      </c>
+      <c r="D18" s="14">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Grants received in advance (unspent)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>156100</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>221900</v>
+      </c>
+      <c r="D19" s="14">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Employee leave provisions</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>166600</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>165900</v>
+      </c>
+      <c r="D20" s="14">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B17" s="16">
-        <f>SUM(B14:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="16">
-        <f>SUM(C14:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="17">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="B21" s="16">
+        <f>SUM(B14:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>SUM(C14:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Net assets</t>
         </is>
       </c>
-      <c r="B18" s="19">
-        <f>B12-B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="19">
-        <f>C12-C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="20">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="B22" s="19">
+        <f>B12-B21</f>
+        <v/>
+      </c>
+      <c r="C22" s="19">
+        <f>C12-C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Accumulated funds</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
-        <v>317330</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>306950</v>
-      </c>
-      <c r="D20" s="20">
-        <f>B20-C20</f>
+      <c r="B24" s="19" t="n">
+        <v>251525</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>241145</v>
+      </c>
+      <c r="D24" s="20">
+        <f>B24-C24</f>
         <v/>
       </c>
     </row>
@@ -2280,7 +2348,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2295,7 +2363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2321,7 +2389,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2446,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>69500</v>
+        <v>73660</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>18400</v>
@@ -2395,10 +2463,10 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>27700</v>
+        <v>30470</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>26100</v>
+        <v>28710</v>
       </c>
       <c r="D8" s="14">
         <f>B8-C8</f>
@@ -2429,7 +2497,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>-46525</v>
+        <v>-51178</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>-36500</v>
@@ -2446,10 +2514,10 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>-96950</v>
+        <v>-74666</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>-93775</v>
+        <v>-74666</v>
       </c>
       <c r="D11" s="14">
         <f>B11-C11</f>
@@ -2457,63 +2525,61 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>GST and PAYG paid (BAS)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B12" s="16">
-        <f>SUM(B6:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="16">
-        <f>SUM(C6:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="17">
-        <f>B12-C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="B13" s="16">
+        <f>SUM(B6:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>SUM(C6:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Investing activities</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Purchase of vehicles and equipment</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="14">
-        <f>B14-C14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Net cash from investing activities</t>
-        </is>
-      </c>
-      <c r="B15" s="16">
-        <f>SUM(B14:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="16">
-        <f>SUM(C14:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="17">
+      <c r="D15" s="14">
         <f>B15-C15</f>
         <v/>
       </c>
@@ -2521,15 +2587,15 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>Net cash from investing activities</t>
         </is>
       </c>
       <c r="B16" s="16">
-        <f>B12+B15</f>
+        <f>SUM(B15:B15)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>C12+C15</f>
+        <f>SUM(C15:C15)</f>
         <v/>
       </c>
       <c r="D16" s="17">
@@ -2540,14 +2606,16 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Cash at start of month</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>525675</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>610000</v>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>B13+B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>C13+C16</f>
+        <v/>
       </c>
       <c r="D17" s="17">
         <f>B17-C17</f>
@@ -2555,21 +2623,38 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Cash at start of month</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>547394</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>610000</v>
+      </c>
+      <c r="D18" s="17">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Cash at end of month</t>
         </is>
       </c>
-      <c r="B18" s="19">
-        <f>B17+B16</f>
-        <v/>
-      </c>
-      <c r="C18" s="19">
-        <f>C17+C16</f>
-        <v/>
-      </c>
-      <c r="D18" s="20">
-        <f>B18-C18</f>
+      <c r="B19" s="19">
+        <f>B18+B17</f>
+        <v/>
+      </c>
+      <c r="C19" s="19">
+        <f>C18+C17</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
+        <f>B19-C19</f>
         <v/>
       </c>
     </row>
@@ -2630,7 +2715,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
+  <conditionalFormatting sqref="D13">
     <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -2667,6 +2752,14 @@
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" priority="25" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2675,7 +2768,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2725,7 +2818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3220,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3146,7 +3239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D194"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3172,7 +3265,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3439,7 @@
     <row r="21">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>(Cash at bank − unspent grant money) ÷ this month's cash spending</t>
+          <t>(Cash at bank − unspent grant money − GST and PAYG owed to the ATO) ÷ a month's cash spending</t>
         </is>
       </c>
     </row>
@@ -3370,10 +3463,10 @@
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>480780</v>
+        <v>527060</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>525675</v>
+        <v>547394</v>
       </c>
     </row>
     <row r="24">
@@ -3392,311 +3485,293 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unrestricted cash</t>
-        </is>
-      </c>
-      <c r="B25" s="22">
-        <f>B23+B24</f>
-        <v/>
-      </c>
-      <c r="C25" s="22">
-        <f>C23+C24</f>
-        <v/>
+          <t>Less GST and PAYG withheld owed to the ATO (paid with the BAS)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>-65523</v>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>-51696</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Unrestricted cash</t>
+        </is>
+      </c>
+      <c r="B26" s="22">
+        <f>B23+B24+B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="22">
+        <f>C23+C24+C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Cash spending in the month (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B27" s="22" t="n">
         <v>162900</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C27" s="22" t="n">
         <v>141200</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B27" s="31">
-        <f>B25/B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="31">
-        <f>C25/C26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="B28" s="31">
+        <f>B26/B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="31">
+        <f>C26/C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Reserves target: 3.0 months.</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30"/>
-    <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Grants ending in the next 6 months</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Grant total − spent to date, for each grant ending soon</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Still to spend</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Housing support (ends 31 Dec 2026)</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n">
-        <v>102300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Housing support (ends 31 Dec 2026)</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>102300</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Digital literacy (ends 31 Mar 2027)</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n">
+        <v>30400</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Mental health first aid (ends 31 Mar 2027)</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n">
+        <v>62800</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Volunteer coordinator (ends 28 Feb 2027)</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B38" s="22" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>Total still to spend</t>
         </is>
       </c>
-      <c r="B36" s="32">
-        <f>B34+B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="B39" s="32">
+        <f>B35+B36+B37+B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Unspent money usually has to be returned, or an extension negotiated, so plan the spending now.</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="27" t="inlineStr">
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="28" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>State Department of Families · $480,000 · Jul 2025 to Jun 2027</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr"/>
-      <c r="B42" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B43" s="22" t="n">
-        <v>480000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="n">
-        <v>306300</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Grant total</t>
         </is>
       </c>
       <c r="B46" s="22" t="n">
-        <v>300000</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Months left</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B47" s="22" t="n">
-        <v>9</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B48" s="22">
-        <f>B43-B45</f>
-        <v/>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n">
+        <v>306300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B51" s="22">
+        <f>B46-B48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B49" s="22">
-        <f>B45-B46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="B52" s="22">
+        <f>B48-B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B50" s="33">
-        <f>B45/B46-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="B53" s="33">
+        <f>B48/B49-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Jul 25</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="n">
-        <v>17363</v>
-      </c>
-      <c r="C54" s="9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D54" s="11">
-        <f>IF(C54=0,"",B54/C54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Aug 25</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n">
-        <v>21144</v>
-      </c>
-      <c r="C55" s="9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D55" s="11">
-        <f>IF(C55=0,"",B55/C55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Sep 25</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n">
-        <v>17537</v>
-      </c>
-      <c r="C56" s="9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D56" s="11">
-        <f>IF(C56=0,"",B56/C56)</f>
-        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B57" s="9" t="n">
-        <v>21925</v>
+        <v>17363</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>20000</v>
@@ -3709,11 +3784,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Aug 25</t>
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>21079</v>
+        <v>21144</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>20000</v>
@@ -3726,11 +3801,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dec 25</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B59" s="9" t="n">
-        <v>19272</v>
+        <v>17537</v>
       </c>
       <c r="C59" s="9" t="n">
         <v>20000</v>
@@ -3743,11 +3818,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jan 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>21157</v>
+        <v>21925</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>20000</v>
@@ -3760,11 +3835,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B61" s="9" t="n">
-        <v>20743</v>
+        <v>21079</v>
       </c>
       <c r="C61" s="9" t="n">
         <v>20000</v>
@@ -3777,11 +3852,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Dec 25</t>
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>16515</v>
+        <v>19272</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>20000</v>
@@ -3794,11 +3869,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Jan 26</t>
         </is>
       </c>
       <c r="B63" s="9" t="n">
-        <v>20451</v>
+        <v>21157</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>20000</v>
@@ -3811,11 +3886,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B64" s="9" t="n">
-        <v>21174</v>
+        <v>20743</v>
       </c>
       <c r="C64" s="9" t="n">
         <v>20000</v>
@@ -3828,11 +3903,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B65" s="9" t="n">
-        <v>20366</v>
+        <v>16515</v>
       </c>
       <c r="C65" s="9" t="n">
         <v>20000</v>
@@ -3845,11 +3920,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B66" s="9" t="n">
-        <v>23274</v>
+        <v>20451</v>
       </c>
       <c r="C66" s="9" t="n">
         <v>20000</v>
@@ -3862,11 +3937,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B67" s="9" t="n">
-        <v>21500</v>
+        <v>21174</v>
       </c>
       <c r="C67" s="9" t="n">
         <v>20000</v>
@@ -3879,11 +3954,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>22800</v>
+        <v>20366</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>20000</v>
@@ -3894,220 +3969,220 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="25" t="inlineStr">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>23274</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D69" s="11">
+        <f>IF(C69=0,"",B69/C69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>21500</v>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D70" s="11">
+        <f>IF(C70=0,"",B70/C70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>22800</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D71" s="11">
+        <f>IF(C71=0,"",B71/C71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B69" s="34">
-        <f>SUM(B54:B68)</f>
-        <v/>
-      </c>
-      <c r="C69" s="34">
-        <f>SUM(C54:C68)</f>
-        <v/>
-      </c>
-      <c r="D69" s="35">
-        <f>IF(C69=0,"",B69/C69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="27" t="inlineStr">
+      <c r="B72" s="34">
+        <f>SUM(B57:B71)</f>
+        <v/>
+      </c>
+      <c r="C72" s="34">
+        <f>SUM(C57:C71)</f>
+        <v/>
+      </c>
+      <c r="D72" s="35">
+        <f>IF(C72=0,"",B72/C72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="28" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>State Housing Program · $360,000 · Jan 2026 to Dec 2026</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr"/>
-      <c r="B74" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr"/>
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="n">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B76" s="22" t="n">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="n">
-        <v>257700</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Grant total</t>
         </is>
       </c>
       <c r="B78" s="22" t="n">
-        <v>270000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Months left</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B79" s="22" t="n">
-        <v>3</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B80" s="22">
-        <f>B75-B77</f>
-        <v/>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="n">
+        <v>257700</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="n">
+        <v>270000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B83" s="22">
+        <f>B78-B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B81" s="22">
-        <f>B77-B78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="29" t="inlineStr">
+      <c r="B84" s="22">
+        <f>B80-B81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B82" s="33">
-        <f>B77/B78-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="B85" s="33">
+        <f>B80/B81-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Jan 26</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="n">
-        <v>30502</v>
-      </c>
-      <c r="C86" s="9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D86" s="11">
-        <f>IF(C86=0,"",B86/C86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Feb 26</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="n">
-        <v>26508</v>
-      </c>
-      <c r="C87" s="9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D87" s="11">
-        <f>IF(C87=0,"",B87/C87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Mar 26</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="n">
-        <v>24832</v>
-      </c>
-      <c r="C88" s="9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D88" s="11">
-        <f>IF(C88=0,"",B88/C88)</f>
-        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Jan 26</t>
         </is>
       </c>
       <c r="B89" s="9" t="n">
-        <v>23730</v>
+        <v>30502</v>
       </c>
       <c r="C89" s="9" t="n">
         <v>30000</v>
@@ -4120,11 +4195,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B90" s="9" t="n">
-        <v>31337</v>
+        <v>26508</v>
       </c>
       <c r="C90" s="9" t="n">
         <v>30000</v>
@@ -4137,11 +4212,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B91" s="9" t="n">
-        <v>29994</v>
+        <v>24832</v>
       </c>
       <c r="C91" s="9" t="n">
         <v>30000</v>
@@ -4154,11 +4229,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B92" s="9" t="n">
-        <v>29097</v>
+        <v>23730</v>
       </c>
       <c r="C92" s="9" t="n">
         <v>30000</v>
@@ -4171,11 +4246,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B93" s="9" t="n">
-        <v>30500</v>
+        <v>31337</v>
       </c>
       <c r="C93" s="9" t="n">
         <v>30000</v>
@@ -4188,11 +4263,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B94" s="9" t="n">
-        <v>31200</v>
+        <v>29994</v>
       </c>
       <c r="C94" s="9" t="n">
         <v>30000</v>
@@ -4203,220 +4278,220 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="25" t="inlineStr">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>29097</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D95" s="11">
+        <f>IF(C95=0,"",B95/C95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>30500</v>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D96" s="11">
+        <f>IF(C96=0,"",B96/C96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>31200</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D97" s="11">
+        <f>IF(C97=0,"",B97/C97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B95" s="34">
-        <f>SUM(B86:B94)</f>
-        <v/>
-      </c>
-      <c r="C95" s="34">
-        <f>SUM(C86:C94)</f>
-        <v/>
-      </c>
-      <c r="D95" s="35">
-        <f>IF(C95=0,"",B95/C95)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98">
-      <c r="A98" s="27" t="inlineStr">
+      <c r="B98" s="34">
+        <f>SUM(B89:B97)</f>
+        <v/>
+      </c>
+      <c r="C98" s="34">
+        <f>SUM(C89:C97)</f>
+        <v/>
+      </c>
+      <c r="D98" s="35">
+        <f>IF(C98=0,"",B98/C98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="27" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="28" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
         <is>
           <t>Federal health program · $120,000 · Apr 2026 to Mar 2027</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr"/>
-      <c r="B100" s="4" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr"/>
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B101" s="22" t="n">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B102" s="22" t="n">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B103" s="22" t="n">
-        <v>57200</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Grant total</t>
         </is>
       </c>
       <c r="B104" s="22" t="n">
-        <v>60000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Months left</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B105" s="22" t="n">
-        <v>6</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B106" s="22">
-        <f>B101-B103</f>
-        <v/>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="n">
+        <v>57200</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B107" s="22" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B108" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B109" s="22">
+        <f>B104-B106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B107" s="22">
-        <f>B103-B104</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="29" t="inlineStr">
+      <c r="B110" s="22">
+        <f>B106-B107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B108" s="33">
-        <f>B103/B104-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109"/>
-    <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="B111" s="33">
+        <f>B106/B107-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B112" s="9" t="n">
-        <v>9584</v>
-      </c>
-      <c r="C112" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D112" s="11">
-        <f>IF(C112=0,"",B112/C112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="n">
-        <v>8950</v>
-      </c>
-      <c r="C113" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D113" s="11">
-        <f>IF(C113=0,"",B113/C113)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="n">
-        <v>9797</v>
-      </c>
-      <c r="C114" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D114" s="11">
-        <f>IF(C114=0,"",B114/C114)</f>
-        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B115" s="9" t="n">
-        <v>8669</v>
+        <v>9584</v>
       </c>
       <c r="C115" s="9" t="n">
         <v>10000</v>
@@ -4429,11 +4504,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B116" s="9" t="n">
-        <v>9400</v>
+        <v>8950</v>
       </c>
       <c r="C116" s="9" t="n">
         <v>10000</v>
@@ -4446,11 +4521,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B117" s="9" t="n">
-        <v>10800</v>
+        <v>9797</v>
       </c>
       <c r="C117" s="9" t="n">
         <v>10000</v>
@@ -4461,220 +4536,220 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="25" t="inlineStr">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="n">
+        <v>8669</v>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D118" s="11">
+        <f>IF(C118=0,"",B118/C118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="n">
+        <v>9400</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D119" s="11">
+        <f>IF(C119=0,"",B119/C119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D120" s="11">
+        <f>IF(C120=0,"",B120/C120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B118" s="34">
-        <f>SUM(B112:B117)</f>
-        <v/>
-      </c>
-      <c r="C118" s="34">
-        <f>SUM(C112:C117)</f>
-        <v/>
-      </c>
-      <c r="D118" s="35">
-        <f>IF(C118=0,"",B118/C118)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121">
-      <c r="A121" s="27" t="inlineStr">
+      <c r="B121" s="34">
+        <f>SUM(B115:B120)</f>
+        <v/>
+      </c>
+      <c r="C121" s="34">
+        <f>SUM(C115:C120)</f>
+        <v/>
+      </c>
+      <c r="D121" s="35">
+        <f>IF(C121=0,"",B121/C121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" s="27" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="28" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="28" t="inlineStr">
         <is>
           <t>Philanthropic foundation · $90,000 · Oct 2025 to Mar 2027</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr"/>
-      <c r="B123" s="4" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr"/>
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B124" s="22" t="n">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B125" s="22" t="n">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B126" s="22" t="n">
-        <v>59600</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Grant total</t>
         </is>
       </c>
       <c r="B127" s="22" t="n">
-        <v>60000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Months left</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B128" s="22" t="n">
-        <v>6</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B129" s="22">
-        <f>B124-B126</f>
-        <v/>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B129" s="22" t="n">
+        <v>59600</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B130" s="22" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B131" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B132" s="22">
+        <f>B127-B129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B130" s="22">
-        <f>B126-B127</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="29" t="inlineStr">
+      <c r="B133" s="22">
+        <f>B129-B130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B131" s="33">
-        <f>B126/B127-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132"/>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
+      <c r="B134" s="33">
+        <f>B129/B130-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Oct 25</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C135" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D135" s="11">
-        <f>IF(C135=0,"",B135/C135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Nov 25</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="n">
-        <v>4585</v>
-      </c>
-      <c r="C136" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D136" s="11">
-        <f>IF(C136=0,"",B136/C136)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Dec 25</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="n">
-        <v>5221</v>
-      </c>
-      <c r="C137" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D137" s="11">
-        <f>IF(C137=0,"",B137/C137)</f>
-        <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jan 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B138" s="9" t="n">
-        <v>4426</v>
+        <v>5160</v>
       </c>
       <c r="C138" s="9" t="n">
         <v>5000</v>
@@ -4687,11 +4762,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B139" s="9" t="n">
-        <v>5408</v>
+        <v>4585</v>
       </c>
       <c r="C139" s="9" t="n">
         <v>5000</v>
@@ -4704,11 +4779,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Dec 25</t>
         </is>
       </c>
       <c r="B140" s="9" t="n">
-        <v>5427</v>
+        <v>5221</v>
       </c>
       <c r="C140" s="9" t="n">
         <v>5000</v>
@@ -4721,11 +4796,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Jan 26</t>
         </is>
       </c>
       <c r="B141" s="9" t="n">
-        <v>5509</v>
+        <v>4426</v>
       </c>
       <c r="C141" s="9" t="n">
         <v>5000</v>
@@ -4738,11 +4813,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B142" s="9" t="n">
-        <v>4635</v>
+        <v>5408</v>
       </c>
       <c r="C142" s="9" t="n">
         <v>5000</v>
@@ -4755,11 +4830,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B143" s="9" t="n">
-        <v>4316</v>
+        <v>5427</v>
       </c>
       <c r="C143" s="9" t="n">
         <v>5000</v>
@@ -4772,11 +4847,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B144" s="9" t="n">
-        <v>4813</v>
+        <v>5509</v>
       </c>
       <c r="C144" s="9" t="n">
         <v>5000</v>
@@ -4789,11 +4864,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B145" s="9" t="n">
-        <v>5200</v>
+        <v>4635</v>
       </c>
       <c r="C145" s="9" t="n">
         <v>5000</v>
@@ -4806,11 +4881,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B146" s="9" t="n">
-        <v>4900</v>
+        <v>4316</v>
       </c>
       <c r="C146" s="9" t="n">
         <v>5000</v>
@@ -4821,427 +4896,427 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="25" t="inlineStr">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="n">
+        <v>4813</v>
+      </c>
+      <c r="C147" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D147" s="11">
+        <f>IF(C147=0,"",B147/C147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D148" s="11">
+        <f>IF(C148=0,"",B148/C148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C149" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D149" s="11">
+        <f>IF(C149=0,"",B149/C149)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B147" s="34">
-        <f>SUM(B135:B146)</f>
-        <v/>
-      </c>
-      <c r="C147" s="34">
-        <f>SUM(C135:C146)</f>
-        <v/>
-      </c>
-      <c r="D147" s="35">
-        <f>IF(C147=0,"",B147/C147)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150">
-      <c r="A150" s="27" t="inlineStr">
+      <c r="B150" s="34">
+        <f>SUM(B138:B149)</f>
+        <v/>
+      </c>
+      <c r="C150" s="34">
+        <f>SUM(C138:C149)</f>
+        <v/>
+      </c>
+      <c r="D150" s="35">
+        <f>IF(C150=0,"",B150/C150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153">
+      <c r="A153" s="27" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="28" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="28" t="inlineStr">
         <is>
           <t>Local council community grant · $48,000 · Jul 2026 to Jun 2027</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr"/>
-      <c r="B152" s="4" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr"/>
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B153" s="22" t="n">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B154" s="22" t="n">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B155" s="22" t="n">
-        <v>12000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Grant total</t>
         </is>
       </c>
       <c r="B156" s="22" t="n">
-        <v>12000</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Months left</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B157" s="22" t="n">
-        <v>9</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B158" s="22">
-        <f>B153-B155</f>
-        <v/>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B158" s="22" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B159" s="22" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B160" s="22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B161" s="22">
+        <f>B156-B158</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B159" s="22">
-        <f>B155-B156</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="29" t="inlineStr">
+      <c r="B162" s="22">
+        <f>B158-B159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B160" s="33">
-        <f>B155/B156-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161"/>
-    <row r="162">
-      <c r="A162" s="10" t="inlineStr">
+      <c r="B163" s="33">
+        <f>B158/B159-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164"/>
+    <row r="165">
+      <c r="A165" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D166" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B164" s="9" t="n">
+      <c r="B167" s="9" t="n">
         <v>3600</v>
       </c>
-      <c r="C164" s="9" t="n">
+      <c r="C167" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D164" s="11">
-        <f>IF(C164=0,"",B164/C164)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="D167" s="11">
+        <f>IF(C167=0,"",B167/C167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B165" s="9" t="n">
+      <c r="B168" s="9" t="n">
         <v>4100</v>
       </c>
-      <c r="C165" s="9" t="n">
+      <c r="C168" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D165" s="11">
-        <f>IF(C165=0,"",B165/C165)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="D168" s="11">
+        <f>IF(C168=0,"",B168/C168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B166" s="9" t="n">
+      <c r="B169" s="9" t="n">
         <v>4300</v>
       </c>
-      <c r="C166" s="9" t="n">
+      <c r="C169" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D166" s="11">
-        <f>IF(C166=0,"",B166/C166)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="25" t="inlineStr">
+      <c r="D169" s="11">
+        <f>IF(C169=0,"",B169/C169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B167" s="34">
-        <f>SUM(B164:B166)</f>
-        <v/>
-      </c>
-      <c r="C167" s="34">
-        <f>SUM(C164:C166)</f>
-        <v/>
-      </c>
-      <c r="D167" s="35">
-        <f>IF(C167=0,"",B167/C167)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170">
-      <c r="A170" s="27" t="inlineStr">
+      <c r="B170" s="34">
+        <f>SUM(B167:B169)</f>
+        <v/>
+      </c>
+      <c r="C170" s="34">
+        <f>SUM(C167:C169)</f>
+        <v/>
+      </c>
+      <c r="D170" s="35">
+        <f>IF(C170=0,"",B170/C170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173">
+      <c r="A173" s="27" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="28" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="28" t="inlineStr">
         <is>
           <t>State volunteering grant · $36,000 · Mar 2026 to Feb 2027</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr"/>
-      <c r="B172" s="4" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr"/>
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>This grant</t>
         </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Grant total</t>
-        </is>
-      </c>
-      <c r="B173" s="22" t="n">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Received from the funder</t>
-        </is>
-      </c>
-      <c r="B174" s="22" t="n">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="B175" s="22" t="n">
-        <v>21000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Budget to date</t>
+          <t>Grant total</t>
         </is>
       </c>
       <c r="B176" s="22" t="n">
-        <v>21000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Months left</t>
+          <t>Received from the funder</t>
         </is>
       </c>
       <c r="B177" s="22" t="n">
-        <v>5</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="B178" s="22">
-        <f>B173-B175</f>
-        <v/>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="B178" s="22" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="B179" s="22" t="n">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+      <c r="B180" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="B181" s="22">
+        <f>B176-B178</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>Over (under) budget to date</t>
         </is>
       </c>
-      <c r="B179" s="22">
-        <f>B175-B176</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="29" t="inlineStr">
+      <c r="B182" s="22">
+        <f>B178-B179</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="29" t="inlineStr">
         <is>
           <t>Over (under) budget, % of budget to date</t>
         </is>
       </c>
-      <c r="B180" s="33">
-        <f>B175/B176-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181"/>
-    <row r="182">
-      <c r="A182" s="10" t="inlineStr">
+      <c r="B183" s="33">
+        <f>B178/B179-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184"/>
+    <row r="185">
+      <c r="A185" s="10" t="inlineStr">
         <is>
           <t>Spend by month against budget</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr">
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="D186" s="4" t="inlineStr">
         <is>
           <t>Spend against budget</t>
         </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Mar 26</t>
-        </is>
-      </c>
-      <c r="B184" s="9" t="n">
-        <v>2932</v>
-      </c>
-      <c r="C184" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D184" s="11">
-        <f>IF(C184=0,"",B184/C184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="n">
-        <v>3555</v>
-      </c>
-      <c r="C185" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D185" s="11">
-        <f>IF(C185=0,"",B185/C185)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="n">
-        <v>2649</v>
-      </c>
-      <c r="C186" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D186" s="11">
-        <f>IF(C186=0,"",B186/C186)</f>
-        <v/>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B187" s="9" t="n">
-        <v>2699</v>
+        <v>2932</v>
       </c>
       <c r="C187" s="9" t="n">
         <v>3000</v>
@@ -5254,11 +5329,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 26</t>
         </is>
       </c>
       <c r="B188" s="9" t="n">
-        <v>3165</v>
+        <v>3555</v>
       </c>
       <c r="C188" s="9" t="n">
         <v>3000</v>
@@ -5271,11 +5346,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B189" s="9" t="n">
-        <v>3000</v>
+        <v>2649</v>
       </c>
       <c r="C189" s="9" t="n">
         <v>3000</v>
@@ -5288,11 +5363,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="B190" s="9" t="n">
-        <v>3000</v>
+        <v>2699</v>
       </c>
       <c r="C190" s="9" t="n">
         <v>3000</v>
@@ -5303,47 +5378,98 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="25" t="inlineStr">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="n">
+        <v>3165</v>
+      </c>
+      <c r="C191" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D191" s="11">
+        <f>IF(C191=0,"",B191/C191)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
+      </c>
+      <c r="B192" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C192" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D192" s="11">
+        <f>IF(C192=0,"",B192/C192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C193" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D193" s="11">
+        <f>IF(C193=0,"",B193/C193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B191" s="34">
-        <f>SUM(B184:B190)</f>
-        <v/>
-      </c>
-      <c r="C191" s="34">
-        <f>SUM(C184:C190)</f>
-        <v/>
-      </c>
-      <c r="D191" s="35">
-        <f>IF(C191=0,"",B191/C191)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
+      <c r="B194" s="34">
+        <f>SUM(B187:B193)</f>
+        <v/>
+      </c>
+      <c r="C194" s="34">
+        <f>SUM(C187:C193)</f>
+        <v/>
+      </c>
+      <c r="D194" s="35">
+        <f>IF(C194=0,"",B194/C194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="7" manualBreakCount="7">
-    <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="39" min="0" max="16383" man="1"/>
-    <brk id="71" min="0" max="16383" man="1"/>
-    <brk id="97" min="0" max="16383" man="1"/>
-    <brk id="120" min="0" max="16383" man="1"/>
-    <brk id="149" min="0" max="16383" man="1"/>
-    <brk id="169" min="0" max="16383" man="1"/>
+    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="42" min="0" max="16383" man="1"/>
+    <brk id="74" min="0" max="16383" man="1"/>
+    <brk id="100" min="0" max="16383" man="1"/>
+    <brk id="123" min="0" max="16383" man="1"/>
+    <brk id="152" min="0" max="16383" man="1"/>
+    <brk id="172" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -5354,7 +5480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5378,7 +5504,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:34am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5740,7 @@
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>cash at bank less unspent grant money</t>
+          <t>cash at bank less unspent grant money, and less GST and PAYG withheld owed to the ATO</t>
         </is>
       </c>
     </row>
@@ -5642,120 +5768,236 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>GST, BAS and payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B31" s="37" t="inlineStr">
-        <is>
-          <t>excluded throughout, for simplicity</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>registered (income over the $150,000 not-for-profit threshold); 10%, accruals basis. The P&amp;L excludes GST; cash, fees receivable and bills include it</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>BAS</t>
+        </is>
+      </c>
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>quarterly, self-lodged: GST on sales − GST credits + PAYG withheld. July to September is due 28 October; October to December, 28 February</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="36" t="inlineStr">
+        <is>
+          <t>Pay runs</t>
+        </is>
+      </c>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>fortnightly on Thursdays: $39,298 gross (a 26th of the year's gross wages); net pay $32,617 and super $4,716 paid on the day; PAYG withheld (about 17% of gross, $6,681) goes with the BAS. Two months a year have three pay runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>12% of gross wages, paid with each pay run (Payday Super, from 1 July 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>Payroll tax</t>
+        </is>
+      </c>
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>none: the charity is exempt for wages paid for its charitable work (assumption to confirm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="36" t="inlineStr">
+        <is>
+          <t>Banking days</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>money only moves on banking days: a payment due on a weekend or Queensland public holiday moves to the next banking day</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="36" t="inlineStr">
+        <is>
+          <t>Donations (assumption to confirm)</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>no GST: a gift isn't payment for anything</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>Program fees (assumption to confirm)</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>taxable: GST included in what's charged</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>Grants (assumption to confirm)</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>taxable supplies under each funding agreement: the funder pays each instalment plus 10% GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>Fundraising events (assumption to confirm)</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>taxable: ticket sales include GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Checks (all passed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>✓ Every subtotal and total adds up</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>✓ Balance sheet balances: assets = liabilities + accumulated funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>✓ Cash flow ends at the cash in the bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>✓ Surplus ties to the movement in accumulated funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>✓ Grant income equals what was spent on each grant</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>✓ Unspent grants equal instalments received less income recognised</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Print check (done before this file was saved)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>✓ The fourth sheet: 1 page, 100% scale, no block split</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>✓ Income and expenditure: 2 pages, 100% scale, no block split</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>✓ Balance sheet: 1 page, 100% scale, no block split</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>✓ Cash flow: 1 page, 100% scale, no block split</t>
+          <t>✓ Every subtotal and total adds up</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>✓ Grants: 1 page, 66% scale, no block split</t>
+          <t>✓ Balance sheet balances: assets = liabilities + accumulated funds</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>✓ Workings: 8 pages, 100% scale, no block split</t>
+          <t>✓ Cash flow ends at the cash in the bank</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
+        <is>
+          <t>✓ Surplus ties to the movement in accumulated funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>✓ Grant income equals what was spent on each grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>✓ Unspent grants equal instalments received less income recognised</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Print check (done before this file was saved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>✓ The fourth sheet: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>✓ Income and expenditure: 2 pages, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>✓ Balance sheet: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>✓ Cash flow: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>✓ Grants: 1 page, 66% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>✓ Workings: 8 pages, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>✓ Assumptions: 2 pages, 100% scale, no block split</t>
         </is>
@@ -5767,14 +6009,14 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:34am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 nfp-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="31" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>